--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-12 22:39（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 01:45（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,24 +1101,47 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1318,13 +1341,13 @@
         <v>0.009000000000000005</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.003545454545454546</v>
+        <v>0.002333333333333333</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>16</v>
@@ -6852,7 +6875,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-12 22:39（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-13 01:45（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,9 +18,9 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$52</f>
+              <f>'資金明細'!$R$2:$R$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 01:45（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 16:19（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -811,19 +811,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -831,35 +831,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$26,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$28,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$J$2:$J$26,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$J$2:$J$28,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$J$2:$J$26,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$J$2:$J$28,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$J$2:$J$26,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$J$2:$J$28,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$26,"&lt;&gt;未平倉",交易明細!$L$2:$L$26,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$28,"&lt;&gt;未平倉",交易明細!$L$2:$L$28,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$26,"做多",交易明細!$B$2:$B$26,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$B$2:$B$28,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -878,19 +878,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -898,35 +898,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$26,交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$26,"做多",交易明細!$J$2:$J$26,"&lt;&gt;未平倉",交易明細!$L$2:$L$26,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"&lt;&gt;未平倉",交易明細!$L$2:$L$28,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$26,"做空",交易明細!$B$2:$B$26,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$B$2:$B$28,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -945,19 +945,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -965,35 +965,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$26,交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$26,"做空",交易明細!$J$2:$J$26,"&lt;&gt;未平倉",交易明細!$L$2:$L$26,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"&lt;&gt;未平倉",交易明細!$L$2:$L$28,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,47 +1101,70 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1305,31 +1328,31 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5344827586206896</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.008894736842105275</v>
+        <v>-0.008241379310344838</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.002111111111111119</v>
+        <v>-0.00620000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.009260869565217404</v>
+        <v>-0.007666666666666678</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>28</v>
@@ -1341,13 +1364,13 @@
         <v>0.009000000000000005</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.002333333333333333</v>
+        <v>0.001173913043478257</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>16</v>
@@ -1421,7 +1444,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R52</f>
+        <f>資金明細!R55</f>
         <v/>
       </c>
     </row>
@@ -1459,7 +1482,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$52)</f>
+        <f>MAX(資金明細!$R$2:$R$55)</f>
         <v/>
       </c>
     </row>
@@ -1478,7 +1501,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$52)</f>
+        <f>MIN(資金明細!$R$2:$R$55)</f>
         <v/>
       </c>
     </row>
@@ -1498,7 +1521,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$52)</f>
+        <f>MIN(資金明細!$X$2:$X$55)</f>
         <v/>
       </c>
     </row>
@@ -1517,7 +1540,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$52,"進場",資金明細!$N$2:$N$52,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$55,"進場",資金明細!$N$2:$N$55,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1536,7 +1559,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$52,"進場",資金明細!$N$2:$N$52,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$55,"進場",資金明細!$N$2:$N$55,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1547,7 +1570,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$52,"出場",資金明細!$N$2:$N$52,"已下單",資金明細!$K$2:$K$52,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$55,"出場",資金明細!$N$2:$N$55,"已下單",資金明細!$K$2:$K$55,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1581,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$26),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$28),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1567,7 +1590,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$52,"出場",資金明細!$N$2:$N$52,"已下單",資金明細!$K$2:$K$52,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$55,"出場",資金明細!$N$2:$N$55,"已下單",資金明細!$K$2:$K$55,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1583,7 +1606,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$52,"出場",資金明細!$N$2:$N$52,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$55,"出場",資金明細!$N$2:$N$55,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1599,7 +1622,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$52)</f>
+        <f>MAX(資金明細!$U$2:$U$55)</f>
         <v/>
       </c>
     </row>
@@ -1615,7 +1638,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$52)</f>
+        <f>MAX(資金明細!$S$2:$S$55)</f>
         <v/>
       </c>
     </row>
@@ -1626,7 +1649,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V52</f>
+        <f>B5*資金明細!V55</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1660,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>0</f>
+        <f>IF(資金明細!N55="已下單",資金明細!O55*交易明細!L28,0)</f>
         <v/>
       </c>
     </row>
@@ -1648,7 +1671,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$52)</f>
+        <f>MAX(資金明細!$Y$2:$Y$55)</f>
         <v/>
       </c>
     </row>
@@ -1670,7 +1693,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$52,MATCH(1,資金明細!$Z$2:$Z$52,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$55,MATCH(1,資金明細!$Z$2:$Z$55,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1681,7 +1704,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$52,"進場",資金明細!$N$2:$N$52,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$55,"進場",資金明細!$N$2:$N$55,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z52"/>
+  <dimension ref="A1:Z55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6792,9 +6815,296 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>46278.08333333334</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="H53" s="20" t="n">
+        <v>1.45436</v>
+      </c>
+      <c r="I53" s="20" t="n">
+        <v>1.3414</v>
+      </c>
+      <c r="J53" s="20" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="19">
+        <f>資金模擬!$B$5*V52</f>
+        <v/>
+      </c>
+      <c r="N53" s="2">
+        <f>IF(Z52=1,"已停止",IF(T52&gt;=M53,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O53" s="19">
+        <f>IF(N53="已下單",M53*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P53" s="4" t="n"/>
+      <c r="Q53" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="13">
+        <f>R52+Q53</f>
+        <v/>
+      </c>
+      <c r="S53" s="19">
+        <f>S52+IF(N53="已下單",M53,0)</f>
+        <v/>
+      </c>
+      <c r="T53" s="19">
+        <f>R53-S53</f>
+        <v/>
+      </c>
+      <c r="U53" s="2">
+        <f>U52+IF(N53="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V53" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R53,0),MAX(V52,FLOOR(MAX(R53,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W53" s="13">
+        <f>MAX(W52,R53)</f>
+        <v/>
+      </c>
+      <c r="X53" s="4">
+        <f>IF(W53&gt;0,R53/W53-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y53" s="19">
+        <f>IF(R53&gt;0,S53*資金模擬!$B$7/R53,0)</f>
+        <v/>
+      </c>
+      <c r="Z53" s="2">
+        <f>IF(OR(Z52=1,R53&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>46278.125</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="H54" s="20" t="n">
+        <v>1.45436</v>
+      </c>
+      <c r="I54" s="20" t="n">
+        <v>1.3414</v>
+      </c>
+      <c r="J54" s="20" t="n">
+        <v>1.45436</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L54" s="5">
+        <f>交易明細!K27</f>
+        <v/>
+      </c>
+      <c r="M54" s="19">
+        <f>M53</f>
+        <v/>
+      </c>
+      <c r="N54" s="2">
+        <f>N53</f>
+        <v/>
+      </c>
+      <c r="O54" s="19">
+        <f>O53</f>
+        <v/>
+      </c>
+      <c r="P54" s="4">
+        <f>交易明細!L27</f>
+        <v/>
+      </c>
+      <c r="Q54" s="13">
+        <f>IF(N54="已下單",O54*P54,0)</f>
+        <v/>
+      </c>
+      <c r="R54" s="13">
+        <f>R53+Q54</f>
+        <v/>
+      </c>
+      <c r="S54" s="19">
+        <f>S53-IF(N54="已下單",M54,0)</f>
+        <v/>
+      </c>
+      <c r="T54" s="19">
+        <f>R54-S54</f>
+        <v/>
+      </c>
+      <c r="U54" s="2">
+        <f>U53-IF(N54="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V54" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R54,0),MAX(V53,FLOOR(MAX(R54,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W54" s="13">
+        <f>MAX(W53,R54)</f>
+        <v/>
+      </c>
+      <c r="X54" s="4">
+        <f>IF(W54&gt;0,R54/W54-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y54" s="19">
+        <f>IF(R54&gt;0,S54*資金模擬!$B$7/R54,0)</f>
+        <v/>
+      </c>
+      <c r="Z54" s="2">
+        <f>IF(OR(Z53=1,R54&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>46278.5</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="H55" s="20" t="n">
+        <v>1.22317</v>
+      </c>
+      <c r="I55" s="20" t="n">
+        <v>1.32405</v>
+      </c>
+      <c r="J55" s="20" t="n"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="19">
+        <f>資金模擬!$B$5*V54</f>
+        <v/>
+      </c>
+      <c r="N55" s="2">
+        <f>IF(Z54=1,"已停止",IF(T54&gt;=M55,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O55" s="19">
+        <f>IF(N55="已下單",M55*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P55" s="4" t="n"/>
+      <c r="Q55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="13">
+        <f>R54+Q55</f>
+        <v/>
+      </c>
+      <c r="S55" s="19">
+        <f>S54+IF(N55="已下單",M55,0)</f>
+        <v/>
+      </c>
+      <c r="T55" s="19">
+        <f>R55-S55</f>
+        <v/>
+      </c>
+      <c r="U55" s="2">
+        <f>U54+IF(N55="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V55" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R55,0),MAX(V54,FLOOR(MAX(R55,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W55" s="13">
+        <f>MAX(W54,R55)</f>
+        <v/>
+      </c>
+      <c r="X55" s="4">
+        <f>IF(W55&gt;0,R55/W55-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y55" s="19">
+        <f>IF(R55&gt;0,S55*資金模擬!$B$7/R55,0)</f>
+        <v/>
+      </c>
+      <c r="Z55" s="2">
+        <f>IF(OR(Z54=1,R55&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z52"/>
-  <conditionalFormatting sqref="K2:K52">
+  <autoFilter ref="A1:Z55"/>
+  <conditionalFormatting sqref="K2:K55">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -6802,7 +7112,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N52">
+  <conditionalFormatting sqref="N2:N55">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -6810,7 +7120,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q52">
+  <conditionalFormatting sqref="Q2:Q55">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -6875,7 +7185,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-13 01:45（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-13 16:19（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7079,7 +7389,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$26),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$28),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7244,7 +7554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9825,9 +10135,205 @@
         <v/>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>46278.08333333334</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>1.45436</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>1.3414</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>46278.125</v>
+      </c>
+      <c r="I27" s="20" t="n">
+        <v>1.45436</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K27" s="5">
+        <f>(H27-D27)*24</f>
+        <v/>
+      </c>
+      <c r="L27" s="4">
+        <f>IF(C27="做多",I27/E27-1,1-I27/E27)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="4" t="n">
+        <v>0.06485671191553544</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>0.0402440441641955</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>0.05724233461869632</v>
+      </c>
+      <c r="Q27" s="22" t="n">
+        <v>358363.9</v>
+      </c>
+      <c r="R27" s="22" t="n">
+        <v>2323206.5163</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="19" t="n">
+        <v>1.628344958438214</v>
+      </c>
+      <c r="V27" s="19" t="n">
+        <v>0.9374999999999999</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>0.1756477719309932</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>0.1489015459723351</v>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>-0.001973460448671305</v>
+      </c>
+      <c r="Z27" s="4" t="n">
+        <v>-0.001188114198741208</v>
+      </c>
+      <c r="AA27" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB27" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC27" s="4">
+        <f>(AB27+2*參數!$B$7)/(AA27+AB27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>46278.5</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>1.22317</v>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>1.32405</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>46278.66666666666</v>
+      </c>
+      <c r="I28" s="20" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K28" s="5">
+        <f>(H28-D28)*24</f>
+        <v/>
+      </c>
+      <c r="L28" s="4">
+        <f>IF(C28="做多",I28/E28-1,1-I28/E28)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>-0.03149001536098317</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>0.04700685788213382</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>-0.05684367988032912</v>
+      </c>
+      <c r="Q28" s="22" t="n">
+        <v>-166098.5</v>
+      </c>
+      <c r="R28" s="22" t="n">
+        <v>1633132.5949</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>0.009516256938937206</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>0.04203013481364004</v>
+      </c>
+      <c r="U28" s="19" t="n">
+        <v>2.452428134930138</v>
+      </c>
+      <c r="V28" s="19" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>-0.03967416397335244</v>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>0.1181818181818182</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>0.001314973745824233</v>
+      </c>
+      <c r="Z28" s="4" t="n">
+        <v>0.001197595179174393</v>
+      </c>
+      <c r="AA28" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB28" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC28" s="4">
+        <f>(AB28+2*參數!$B$7)/(AA28+AB28)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC26"/>
-  <conditionalFormatting sqref="J2:J26">
+  <autoFilter ref="A1:AC28"/>
+  <conditionalFormatting sqref="J2:J28">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -9848,7 +10354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9934,27 +10440,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A2,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A2,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$26,$A2,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A2,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A2,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -9962,19 +10468,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A2,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A2,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A2,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A2,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9985,27 +10491,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A3,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A3,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$26,$A3,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A3,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A3,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -10013,19 +10519,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A3,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A3,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A3,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A3,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10036,27 +10542,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A4,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A4,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$26,$A4,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A4,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A4,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -10064,19 +10570,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A4,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A4,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A4,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A4,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10087,27 +10593,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A5,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A5,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$26,$A5,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A5,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A5,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -10115,19 +10621,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A5,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A5,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A5,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A5,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10138,27 +10644,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A6,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A6,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$26,$A6,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A6,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A6,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -10166,19 +10672,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A6,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A6,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A6,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A6,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10189,27 +10695,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A7,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A7,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$26,$A7,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A7,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A7,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -10217,19 +10723,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A7,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A7,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A7,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A7,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10240,27 +10746,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A8,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A8,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$26,$A8,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A8,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A8,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -10268,50 +10774,50 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A8,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A8,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A8,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A8,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ACE_USDT_PERP</t>
+          <t>RIVER_USDT_PERP</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A9,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A9,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$26,$A9,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A9,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A9,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -10319,50 +10825,50 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A9,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A9,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A9,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A9,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ARB_USDT_PERP</t>
+          <t>ACE_USDT_PERP</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A10,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A10,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$26,$A10,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A10,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A10,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -10370,50 +10876,50 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A10,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A10,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A10,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A10,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DASH_USDT_PERP</t>
+          <t>ARB_USDT_PERP</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A11,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A11,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$26,$A11,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A11,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A11,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -10421,50 +10927,50 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A11,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A11,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A11,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A11,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>IOST_USDT_PERP</t>
+          <t>DASH_USDT_PERP</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A12,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A12,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$26,$A12,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A12,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A12,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -10472,50 +10978,50 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A12,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A12,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A12,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A12,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CASHCAT_USDT_PERP</t>
+          <t>IOST_USDT_PERP</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A13,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A13,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$26,$A13,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A13,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A13,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -10523,50 +11029,50 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A13,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A13,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A13,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A13,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AKE_USDT_PERP</t>
+          <t>CASHCAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A14,交易明細!$C$2:$C$26,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$C$2:$C$28,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A14,交易明細!$C$2:$C$26,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$C$2:$C$28,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$26,$A14,交易明細!$J$2:$J$26,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A14,交易明細!$J$2:$J$26,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A14,交易明細!$J$2:$J$26,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -10574,24 +11080,75 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A14,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$26,交易明細!$B$2:$B$26,$A14,交易明細!$J$2:$J$26,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$26,交易明細!$B$2:$B$26,$A14,交易明細!$J$2:$J$26,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$26,$A14,交易明細!$J$2:$J$26,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>AKE_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$C$2:$C$28,"做多")</f>
+        <v/>
+      </c>
+      <c r="D15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$C$2:$C$28,"做空")</f>
+        <v/>
+      </c>
+      <c r="E15" s="2">
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"止損")</f>
+        <v/>
+      </c>
+      <c r="H15" s="4">
+        <f>IFERROR(F15/E15,0)</f>
+        <v/>
+      </c>
+      <c r="I15" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J15" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K15" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L14"/>
+  <autoFilter ref="A1:L15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16410,7 +16967,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C321" s="2" t="inlineStr"/>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D321" s="2" t="n"/>
       <c r="E321" s="20" t="n"/>
       <c r="F321" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,7 +18,7 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$55</f>
+              <f>'資金明細'!$R$2:$R$56</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 16:19（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 17:04（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,16 +1101,16 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -1124,47 +1124,70 @@
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1346,13 +1369,13 @@
         <v>-0.00620000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.007666666666666678</v>
+        <v>-0.00620000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>28</v>
@@ -1444,7 +1467,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R55</f>
+        <f>資金明細!R56</f>
         <v/>
       </c>
     </row>
@@ -1482,7 +1505,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$55)</f>
+        <f>MAX(資金明細!$R$2:$R$56)</f>
         <v/>
       </c>
     </row>
@@ -1501,7 +1524,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$55)</f>
+        <f>MIN(資金明細!$R$2:$R$56)</f>
         <v/>
       </c>
     </row>
@@ -1521,7 +1544,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$55)</f>
+        <f>MIN(資金明細!$X$2:$X$56)</f>
         <v/>
       </c>
     </row>
@@ -1540,7 +1563,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$55,"進場",資金明細!$N$2:$N$55,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$56,"進場",資金明細!$N$2:$N$56,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1559,7 +1582,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$55,"進場",資金明細!$N$2:$N$55,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$56,"進場",資金明細!$N$2:$N$56,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1570,7 +1593,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$55,"出場",資金明細!$N$2:$N$55,"已下單",資金明細!$K$2:$K$55,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$56,"出場",資金明細!$N$2:$N$56,"已下單",資金明細!$K$2:$K$56,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1590,7 +1613,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$55,"出場",資金明細!$N$2:$N$55,"已下單",資金明細!$K$2:$K$55,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$56,"出場",資金明細!$N$2:$N$56,"已下單",資金明細!$K$2:$K$56,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1606,7 +1629,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$55,"出場",資金明細!$N$2:$N$55,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$56,"出場",資金明細!$N$2:$N$56,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1622,7 +1645,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$55)</f>
+        <f>MAX(資金明細!$U$2:$U$56)</f>
         <v/>
       </c>
     </row>
@@ -1638,7 +1661,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$55)</f>
+        <f>MAX(資金明細!$S$2:$S$56)</f>
         <v/>
       </c>
     </row>
@@ -1649,7 +1672,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V55</f>
+        <f>B5*資金明細!V56</f>
         <v/>
       </c>
     </row>
@@ -1660,7 +1683,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>IF(資金明細!N55="已下單",資金明細!O55*交易明細!L28,0)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -1671,7 +1694,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$55)</f>
+        <f>MAX(資金明細!$Y$2:$Y$56)</f>
         <v/>
       </c>
     </row>
@@ -1693,7 +1716,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$55,MATCH(1,資金明細!$Z$2:$Z$55,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$56,MATCH(1,資金明細!$Z$2:$Z$56,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1704,7 +1727,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$55,"進場",資金明細!$N$2:$N$55,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$56,"進場",資金明細!$N$2:$N$56,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1769,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z55"/>
+  <dimension ref="A1:Z56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7043,11 +7066,7 @@
         <v>1.32405</v>
       </c>
       <c r="J55" s="20" t="n"/>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K55" s="2" t="n"/>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="19">
         <f>資金模擬!$B$5*V54</f>
@@ -7102,9 +7121,112 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>46278.70833333334</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="H56" s="20" t="n">
+        <v>1.22317</v>
+      </c>
+      <c r="I56" s="20" t="n">
+        <v>1.32405</v>
+      </c>
+      <c r="J56" s="20" t="n">
+        <v>1.22317</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L56" s="5">
+        <f>交易明細!K28</f>
+        <v/>
+      </c>
+      <c r="M56" s="19">
+        <f>M55</f>
+        <v/>
+      </c>
+      <c r="N56" s="2">
+        <f>N55</f>
+        <v/>
+      </c>
+      <c r="O56" s="19">
+        <f>O55</f>
+        <v/>
+      </c>
+      <c r="P56" s="4">
+        <f>交易明細!L28</f>
+        <v/>
+      </c>
+      <c r="Q56" s="13">
+        <f>IF(N56="已下單",O56*P56,0)</f>
+        <v/>
+      </c>
+      <c r="R56" s="13">
+        <f>R55+Q56</f>
+        <v/>
+      </c>
+      <c r="S56" s="19">
+        <f>S55-IF(N56="已下單",M56,0)</f>
+        <v/>
+      </c>
+      <c r="T56" s="19">
+        <f>R56-S56</f>
+        <v/>
+      </c>
+      <c r="U56" s="2">
+        <f>U55-IF(N56="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V56" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R56,0),MAX(V55,FLOOR(MAX(R56,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W56" s="13">
+        <f>MAX(W55,R56)</f>
+        <v/>
+      </c>
+      <c r="X56" s="4">
+        <f>IF(W56&gt;0,R56/W56-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y56" s="19">
+        <f>IF(R56&gt;0,S56*資金模擬!$B$7/R56,0)</f>
+        <v/>
+      </c>
+      <c r="Z56" s="2">
+        <f>IF(OR(Z55=1,R56&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z55"/>
-  <conditionalFormatting sqref="K2:K55">
+  <autoFilter ref="A1:Z56"/>
+  <conditionalFormatting sqref="K2:K56">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -7112,7 +7234,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N55">
+  <conditionalFormatting sqref="N2:N56">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -7120,7 +7242,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q55">
+  <conditionalFormatting sqref="Q2:Q56">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -7185,7 +7307,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-13 16:19（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-13 17:04（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -10258,14 +10380,14 @@
         <v>1.32405</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="I28" s="20" t="n">
-        <v>1.272</v>
+        <v>1.22317</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K28" s="5">
@@ -10276,11 +10398,7 @@
         <f>IF(C28="做多",I28/E28-1,1-I28/E28)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="4" t="n">
         <v>-0.03149001536098317</v>
       </c>
@@ -10297,7 +10415,7 @@
         <v>1633132.5949</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.009516256938937206</v>
+        <v>0.03</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.04203013481364004</v>
@@ -16967,11 +17085,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C321" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C321" s="2" t="inlineStr"/>
       <c r="D321" s="2" t="n"/>
       <c r="E321" s="20" t="n"/>
       <c r="F321" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 17:04（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 20:05（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1113,27 +1113,27 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -1147,47 +1147,70 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1351,13 +1374,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5344827586206896</v>
+        <v>0.55</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.008241379310344838</v>
+        <v>-0.00700000000000001</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>25</v>
@@ -1387,13 +1410,13 @@
         <v>0.009000000000000005</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6595744680851063</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.001173913043478257</v>
+        <v>0.001765957446808508</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>16</v>
@@ -7307,7 +7330,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-13 17:04（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-13 20:05（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,9 +18,9 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$56</f>
+              <f>'資金明細'!$R$2:$R$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-13 20:05（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 00:24（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -811,19 +811,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -831,35 +831,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$28,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$29,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$J$2:$J$28,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$J$2:$J$29,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$J$2:$J$28,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$J$2:$J$29,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$J$2:$J$28,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$J$2:$J$29,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$28,"&lt;&gt;未平倉",交易明細!$L$2:$L$28,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$29,"&lt;&gt;未平倉",交易明細!$L$2:$L$29,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$B$2:$B$28,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$B$2:$B$29,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -878,19 +878,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -898,35 +898,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$28,"做多",交易明細!$J$2:$J$28,"&lt;&gt;未平倉",交易明細!$L$2:$L$28,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"&lt;&gt;未平倉",交易明細!$L$2:$L$29,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$B$2:$B$28,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$B$2:$B$29,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -945,19 +945,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -965,35 +965,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$28,"做空",交易明細!$J$2:$J$28,"&lt;&gt;未平倉",交易明細!$L$2:$L$28,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"&lt;&gt;未平倉",交易明細!$L$2:$L$29,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,33 +1101,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1136,27 +1136,27 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -1170,47 +1170,70 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1259,7 +1282,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>近 1 個月最佳區間：5%–6%（每筆 +0.90%）</t>
+          <t>近 1 個月最佳區間：5%–6%（每筆 +0.77%）</t>
         </is>
       </c>
     </row>
@@ -1374,13 +1397,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.55</v>
+        <v>0.5645161290322581</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.00700000000000001</v>
+        <v>-0.005838709677419364</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>25</v>
@@ -1401,13 +1424,13 @@
         <v>-0.00620000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.75</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.009000000000000005</v>
+        <v>0.00766666666666667</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>47</v>
@@ -1490,7 +1513,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R56</f>
+        <f>資金明細!R58</f>
         <v/>
       </c>
     </row>
@@ -1528,7 +1551,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$56)</f>
+        <f>MAX(資金明細!$R$2:$R$58)</f>
         <v/>
       </c>
     </row>
@@ -1547,7 +1570,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$56)</f>
+        <f>MIN(資金明細!$R$2:$R$58)</f>
         <v/>
       </c>
     </row>
@@ -1567,7 +1590,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$56)</f>
+        <f>MIN(資金明細!$X$2:$X$58)</f>
         <v/>
       </c>
     </row>
@@ -1586,7 +1609,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$56,"進場",資金明細!$N$2:$N$56,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$58,"進場",資金明細!$N$2:$N$58,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1605,7 +1628,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$56,"進場",資金明細!$N$2:$N$56,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$58,"進場",資金明細!$N$2:$N$58,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1616,7 +1639,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$56,"出場",資金明細!$N$2:$N$56,"已下單",資金明細!$K$2:$K$56,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$58,"出場",資金明細!$N$2:$N$58,"已下單",資金明細!$K$2:$K$58,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1627,7 +1650,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$28),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$29),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1636,7 +1659,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$56,"出場",資金明細!$N$2:$N$56,"已下單",資金明細!$K$2:$K$56,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$58,"出場",資金明細!$N$2:$N$58,"已下單",資金明細!$K$2:$K$58,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1652,7 +1675,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$56,"出場",資金明細!$N$2:$N$56,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$58,"出場",資金明細!$N$2:$N$58,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1668,7 +1691,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$56)</f>
+        <f>MAX(資金明細!$U$2:$U$58)</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1707,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$56)</f>
+        <f>MAX(資金明細!$S$2:$S$58)</f>
         <v/>
       </c>
     </row>
@@ -1695,7 +1718,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V56</f>
+        <f>B5*資金明細!V58</f>
         <v/>
       </c>
     </row>
@@ -1717,7 +1740,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$56)</f>
+        <f>MAX(資金明細!$Y$2:$Y$58)</f>
         <v/>
       </c>
     </row>
@@ -1739,7 +1762,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$56,MATCH(1,資金明細!$Z$2:$Z$56,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$58,MATCH(1,資金明細!$Z$2:$Z$58,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1750,7 +1773,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$56,"進場",資金明細!$N$2:$N$56,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$58,"進場",資金明細!$N$2:$N$58,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1815,7 +1838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z56"/>
+  <dimension ref="A1:Z58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7247,9 +7270,202 @@
         <v/>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>46278.95833333334</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G57" s="20" t="n">
+        <v>0.06897</v>
+      </c>
+      <c r="H57" s="20" t="n">
+        <v>0.07103910000000001</v>
+      </c>
+      <c r="I57" s="20" t="n">
+        <v>0.0655215</v>
+      </c>
+      <c r="J57" s="20" t="n"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="19">
+        <f>資金模擬!$B$5*V56</f>
+        <v/>
+      </c>
+      <c r="N57" s="2">
+        <f>IF(Z56=1,"已停止",IF(T56&gt;=M57,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O57" s="19">
+        <f>IF(N57="已下單",M57*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="13">
+        <f>R56+Q57</f>
+        <v/>
+      </c>
+      <c r="S57" s="19">
+        <f>S56+IF(N57="已下單",M57,0)</f>
+        <v/>
+      </c>
+      <c r="T57" s="19">
+        <f>R57-S57</f>
+        <v/>
+      </c>
+      <c r="U57" s="2">
+        <f>U56+IF(N57="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V57" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R57,0),MAX(V56,FLOOR(MAX(R57,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W57" s="13">
+        <f>MAX(W56,R57)</f>
+        <v/>
+      </c>
+      <c r="X57" s="4">
+        <f>IF(W57&gt;0,R57/W57-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y57" s="19">
+        <f>IF(R57&gt;0,S57*資金模擬!$B$7/R57,0)</f>
+        <v/>
+      </c>
+      <c r="Z57" s="2">
+        <f>IF(OR(Z56=1,R57&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G58" s="20" t="n">
+        <v>0.06897</v>
+      </c>
+      <c r="H58" s="20" t="n">
+        <v>0.07103910000000001</v>
+      </c>
+      <c r="I58" s="20" t="n">
+        <v>0.0655215</v>
+      </c>
+      <c r="J58" s="20" t="n">
+        <v>0.07103910000000001</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L58" s="5">
+        <f>交易明細!K29</f>
+        <v/>
+      </c>
+      <c r="M58" s="19">
+        <f>M57</f>
+        <v/>
+      </c>
+      <c r="N58" s="2">
+        <f>N57</f>
+        <v/>
+      </c>
+      <c r="O58" s="19">
+        <f>O57</f>
+        <v/>
+      </c>
+      <c r="P58" s="4">
+        <f>交易明細!L29</f>
+        <v/>
+      </c>
+      <c r="Q58" s="13">
+        <f>IF(N58="已下單",O58*P58,0)</f>
+        <v/>
+      </c>
+      <c r="R58" s="13">
+        <f>R57+Q58</f>
+        <v/>
+      </c>
+      <c r="S58" s="19">
+        <f>S57-IF(N58="已下單",M58,0)</f>
+        <v/>
+      </c>
+      <c r="T58" s="19">
+        <f>R58-S58</f>
+        <v/>
+      </c>
+      <c r="U58" s="2">
+        <f>U57-IF(N58="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V58" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R58,0),MAX(V57,FLOOR(MAX(R58,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W58" s="13">
+        <f>MAX(W57,R58)</f>
+        <v/>
+      </c>
+      <c r="X58" s="4">
+        <f>IF(W58&gt;0,R58/W58-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y58" s="19">
+        <f>IF(R58&gt;0,S58*資金模擬!$B$7/R58,0)</f>
+        <v/>
+      </c>
+      <c r="Z58" s="2">
+        <f>IF(OR(Z57=1,R58&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z56"/>
-  <conditionalFormatting sqref="K2:K56">
+  <autoFilter ref="A1:Z58"/>
+  <conditionalFormatting sqref="K2:K58">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -7257,7 +7473,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N56">
+  <conditionalFormatting sqref="N2:N58">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -7265,7 +7481,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q56">
+  <conditionalFormatting sqref="Q2:Q58">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -7330,7 +7546,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-13 20:05（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 00:24（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7534,7 +7750,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$28),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$29),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7699,7 +7915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10472,9 +10688,105 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>46278.95833333334</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>0.06897</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0.07103910000000001</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0.0655215</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I29" s="20" t="n">
+        <v>0.07103910000000001</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K29" s="5">
+        <f>(H29-D29)*24</f>
+        <v/>
+      </c>
+      <c r="L29" s="4">
+        <f>IF(C29="做多",I29/E29-1,1-I29/E29)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="4" t="n">
+        <v>0.0401146131805159</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>0.04984835563975233</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>0.02012291172098601</v>
+      </c>
+      <c r="Q29" s="22" t="n">
+        <v>1513283</v>
+      </c>
+      <c r="R29" s="22" t="n">
+        <v>2656323.83996</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="19" t="n">
+        <v>2.228271138805124</v>
+      </c>
+      <c r="V29" s="19" t="n">
+        <v>0.6235827664399103</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>0.118889060129945</v>
+      </c>
+      <c r="X29" s="4" t="n">
+        <v>-0.04008350730688925</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>0.004704889882924723</v>
+      </c>
+      <c r="Z29" s="4" t="n">
+        <v>0.001557067200726125</v>
+      </c>
+      <c r="AA29" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB29" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC29" s="4">
+        <f>(AB29+2*參數!$B$7)/(AA29+AB29)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC28"/>
-  <conditionalFormatting sqref="J2:J28">
+  <autoFilter ref="A1:AC29"/>
+  <conditionalFormatting sqref="J2:J29">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -10495,7 +10807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10581,27 +10893,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -10609,19 +10921,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A2,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10632,27 +10944,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -10660,19 +10972,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A3,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10683,27 +10995,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -10711,19 +11023,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A4,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10734,27 +11046,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -10762,19 +11074,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A5,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10785,27 +11097,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -10813,19 +11125,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A6,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10836,27 +11148,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -10864,19 +11176,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A7,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10887,27 +11199,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -10915,19 +11227,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A8,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10938,27 +11250,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -10966,19 +11278,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A9,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10989,27 +11301,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -11017,19 +11329,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A10,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11040,27 +11352,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -11068,19 +11380,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A11,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11091,27 +11403,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -11119,19 +11431,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A12,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11142,27 +11454,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -11170,19 +11482,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A13,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11193,27 +11505,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -11221,19 +11533,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A14,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11244,27 +11556,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$C$2:$C$28,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$C$2:$C$29,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$C$2:$C$28,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$C$2:$C$29,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -11272,24 +11584,75 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$28,交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$28,交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$28,$A15,交易明細!$J$2:$J$28,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$C$2:$C$29,"做多")</f>
+        <v/>
+      </c>
+      <c r="D16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$C$2:$C$29,"做空")</f>
+        <v/>
+      </c>
+      <c r="E16" s="2">
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"止損")</f>
+        <v/>
+      </c>
+      <c r="H16" s="4">
+        <f>IFERROR(F16/E16,0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J16" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K16" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L15"/>
+  <autoFilter ref="A1:L16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 00:24（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 03:31（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,56 +1101,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1159,27 +1159,27 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -1193,47 +1193,70 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7546,7 +7569,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 00:24（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 03:31（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 03:31（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 06:27（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1119,61 +1119,61 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1182,27 +1182,27 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -1216,47 +1216,70 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7569,7 +7592,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 03:31（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 06:27（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 06:27（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 09:11（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1119,15 +1119,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1142,61 +1142,61 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1205,27 +1205,27 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
@@ -1239,47 +1239,70 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1328,7 +1351,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>近 1 個月最佳區間：5%–6%（每筆 +0.77%）</t>
+          <t>近 1 個月最佳區間：5%–6%（每筆 +0.84%）</t>
         </is>
       </c>
     </row>
@@ -1443,13 +1466,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.005838709677419364</v>
+        <v>-0.005285714285714294</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>25</v>
@@ -1470,13 +1493,13 @@
         <v>-0.00620000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.00766666666666667</v>
+        <v>0.008354838709677423</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>47</v>
@@ -7592,7 +7615,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 06:27（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 09:11（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 09:11（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 14:23（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1119,15 +1119,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1142,15 +1142,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1165,61 +1165,61 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1228,27 +1228,27 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -1262,47 +1262,70 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1351,7 +1374,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>近 1 個月最佳區間：5%–6%（每筆 +0.84%）</t>
+          <t>近 1 個月最佳區間：5%–6%（每筆 +0.65%）</t>
         </is>
       </c>
     </row>
@@ -1466,22 +1489,22 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5625</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.005285714285714294</v>
+        <v>-0.006000000000000009</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.00620000000000001</v>
+        <v>-0.004846153846153855</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>25</v>
@@ -1493,13 +1516,13 @@
         <v>-0.00620000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.71875</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.008354838709677423</v>
+        <v>0.006500000000000002</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>47</v>
@@ -7615,7 +7638,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 09:11（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 14:23（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 14:23（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 22:10（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1119,15 +1119,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1142,15 +1142,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1165,15 +1165,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1188,61 +1188,61 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1251,27 +1251,27 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -1285,47 +1285,70 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1374,7 +1397,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>近 1 個月最佳區間：5%–6%（每筆 +0.65%）</t>
+          <t>近 1 個月最佳區間：5%–6%（每筆 +0.55%）</t>
         </is>
       </c>
     </row>
@@ -1498,13 +1521,13 @@
         <v>-0.006000000000000009</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.004846153846153855</v>
+        <v>-0.004103448275862076</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>25</v>
@@ -1516,13 +1539,13 @@
         <v>-0.00620000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.71875</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.006500000000000002</v>
+        <v>0.005470588235294119</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>47</v>
@@ -1534,13 +1557,13 @@
         <v>0.001765957446808508</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.001000000000000008</v>
+        <v>0.002333333333333329</v>
       </c>
     </row>
   </sheetData>
@@ -7638,7 +7661,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 14:23（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-14 22:10（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,8 +18,8 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$58</f>
+              <f>'資金明細'!$R$2:$R$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-14 22:10（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 03:26（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -811,19 +811,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -831,35 +831,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$29,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$30,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$J$2:$J$29,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$J$2:$J$30,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$J$2:$J$29,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$J$2:$J$30,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$J$2:$J$29,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$J$2:$J$30,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$29,"&lt;&gt;未平倉",交易明細!$L$2:$L$29,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$30,"&lt;&gt;未平倉",交易明細!$L$2:$L$30,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$B$2:$B$29,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$B$2:$B$30,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -878,19 +878,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -898,35 +898,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$29,"做多",交易明細!$J$2:$J$29,"&lt;&gt;未平倉",交易明細!$L$2:$L$29,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"&lt;&gt;未平倉",交易明細!$L$2:$L$30,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$B$2:$B$29,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$B$2:$B$30,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -945,19 +945,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -965,35 +965,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$29,"做空",交易明細!$J$2:$J$29,"&lt;&gt;未平倉",交易明細!$L$2:$L$29,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"&lt;&gt;未平倉",交易明細!$L$2:$L$30,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,16 +1101,16 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -1119,15 +1119,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1142,15 +1142,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1165,15 +1165,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1188,15 +1188,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1211,61 +1211,61 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1274,27 +1274,27 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
@@ -1308,47 +1308,70 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1521,13 +1544,13 @@
         <v>-0.006000000000000009</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.004103448275862076</v>
+        <v>-0.003000000000000007</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>25</v>
@@ -1628,7 +1651,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R58</f>
+        <f>資金明細!R59</f>
         <v/>
       </c>
     </row>
@@ -1666,7 +1689,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$58)</f>
+        <f>MAX(資金明細!$R$2:$R$59)</f>
         <v/>
       </c>
     </row>
@@ -1685,7 +1708,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$58)</f>
+        <f>MIN(資金明細!$R$2:$R$59)</f>
         <v/>
       </c>
     </row>
@@ -1705,7 +1728,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$58)</f>
+        <f>MIN(資金明細!$X$2:$X$59)</f>
         <v/>
       </c>
     </row>
@@ -1724,7 +1747,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$58,"進場",資金明細!$N$2:$N$58,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$59,"進場",資金明細!$N$2:$N$59,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1743,7 +1766,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$58,"進場",資金明細!$N$2:$N$58,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$59,"進場",資金明細!$N$2:$N$59,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1754,7 +1777,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$58,"出場",資金明細!$N$2:$N$58,"已下單",資金明細!$K$2:$K$58,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$59,"出場",資金明細!$N$2:$N$59,"已下單",資金明細!$K$2:$K$59,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1765,7 +1788,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$29),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$30),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1774,7 +1797,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$58,"出場",資金明細!$N$2:$N$58,"已下單",資金明細!$K$2:$K$58,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$59,"出場",資金明細!$N$2:$N$59,"已下單",資金明細!$K$2:$K$59,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1790,7 +1813,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$58,"出場",資金明細!$N$2:$N$58,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$59,"出場",資金明細!$N$2:$N$59,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1806,7 +1829,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$58)</f>
+        <f>MAX(資金明細!$U$2:$U$59)</f>
         <v/>
       </c>
     </row>
@@ -1822,7 +1845,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$58)</f>
+        <f>MAX(資金明細!$S$2:$S$59)</f>
         <v/>
       </c>
     </row>
@@ -1833,7 +1856,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V58</f>
+        <f>B5*資金明細!V59</f>
         <v/>
       </c>
     </row>
@@ -1844,7 +1867,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>0</f>
+        <f>IF(資金明細!N59="已下單",資金明細!O59*交易明細!L30,0)</f>
         <v/>
       </c>
     </row>
@@ -1855,7 +1878,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$58)</f>
+        <f>MAX(資金明細!$Y$2:$Y$59)</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1900,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$58,MATCH(1,資金明細!$Z$2:$Z$58,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$59,MATCH(1,資金明細!$Z$2:$Z$59,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1888,7 +1911,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$58,"進場",資金明細!$N$2:$N$58,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$59,"進場",資金明細!$N$2:$N$59,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1953,7 +1976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z58"/>
+  <dimension ref="A1:Z59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7578,9 +7601,103 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>46280.08333333334</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G59" s="20" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="H59" s="20" t="n">
+        <v>0.2217281</v>
+      </c>
+      <c r="I59" s="20" t="n">
+        <v>0.2045065</v>
+      </c>
+      <c r="J59" s="20" t="n"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="19">
+        <f>資金模擬!$B$5*V58</f>
+        <v/>
+      </c>
+      <c r="N59" s="2">
+        <f>IF(Z58=1,"已停止",IF(T58&gt;=M59,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O59" s="19">
+        <f>IF(N59="已下單",M59*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P59" s="4" t="n"/>
+      <c r="Q59" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="13">
+        <f>R58+Q59</f>
+        <v/>
+      </c>
+      <c r="S59" s="19">
+        <f>S58+IF(N59="已下單",M59,0)</f>
+        <v/>
+      </c>
+      <c r="T59" s="19">
+        <f>R59-S59</f>
+        <v/>
+      </c>
+      <c r="U59" s="2">
+        <f>U58+IF(N59="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V59" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R59,0),MAX(V58,FLOOR(MAX(R59,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W59" s="13">
+        <f>MAX(W58,R59)</f>
+        <v/>
+      </c>
+      <c r="X59" s="4">
+        <f>IF(W59&gt;0,R59/W59-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y59" s="19">
+        <f>IF(R59&gt;0,S59*資金模擬!$B$7/R59,0)</f>
+        <v/>
+      </c>
+      <c r="Z59" s="2">
+        <f>IF(OR(Z58=1,R59&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z58"/>
-  <conditionalFormatting sqref="K2:K58">
+  <autoFilter ref="A1:Z59"/>
+  <conditionalFormatting sqref="K2:K59">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -7588,7 +7705,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N58">
+  <conditionalFormatting sqref="N2:N59">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -7596,7 +7713,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q58">
+  <conditionalFormatting sqref="Q2:Q59">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -7661,7 +7778,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-14 22:10（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 03:26（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7865,7 +7982,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$29),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$30),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8030,7 +8147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10899,9 +11016,109 @@
         <v/>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>46280.08333333334</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>0.2217281</v>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>0.2045065</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>46280.125</v>
+      </c>
+      <c r="I30" s="20" t="n">
+        <v>0.21967</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K30" s="5">
+        <f>(H30-D30)*24</f>
+        <v/>
+      </c>
+      <c r="L30" s="4">
+        <f>IF(C30="做多",I30/E30-1,1-I30/E30)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0.07694231827505127</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>0.04129466730861369</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>0.04722917472386601</v>
+      </c>
+      <c r="Q30" s="22" t="n">
+        <v>57563</v>
+      </c>
+      <c r="R30" s="22" t="n">
+        <v>2142958.19727</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>0.02870813397129202</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>0.01337854787011661</v>
+      </c>
+      <c r="U30" s="19" t="n">
+        <v>2.695897368776979</v>
+      </c>
+      <c r="V30" s="19" t="n">
+        <v>0.8418891170431212</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>-0.03711019445659591</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>-0.01193372194427877</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>0.002349919531133837</v>
+      </c>
+      <c r="Z30" s="4" t="n">
+        <v>0.01492736573107156</v>
+      </c>
+      <c r="AA30" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB30" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC30" s="4">
+        <f>(AB30+2*參數!$B$7)/(AA30+AB30)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC29"/>
-  <conditionalFormatting sqref="J2:J29">
+  <autoFilter ref="A1:AC30"/>
+  <conditionalFormatting sqref="J2:J30">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -11008,27 +11225,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -11036,50 +11253,50 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A2,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>UAI_USDT_PERP</t>
+          <t>USELESS_USDT_PERP</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -11087,50 +11304,50 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A3,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VVV_USDT_PERP</t>
+          <t>UAI_USDT_PERP</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -11138,50 +11355,50 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A4,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>USELESS_USDT_PERP</t>
+          <t>VVV_USDT_PERP</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -11189,19 +11406,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A5,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11212,27 +11429,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -11240,19 +11457,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A6,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11263,27 +11480,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -11291,19 +11508,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A7,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11314,27 +11531,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -11342,19 +11559,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A8,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11365,27 +11582,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -11393,19 +11610,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A9,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11416,27 +11633,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -11444,19 +11661,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A10,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11467,27 +11684,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -11495,19 +11712,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A11,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11518,27 +11735,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -11546,19 +11763,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A12,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11569,27 +11786,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -11597,19 +11814,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A13,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11620,27 +11837,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -11648,19 +11865,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A14,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11671,27 +11888,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -11699,19 +11916,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A15,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11722,27 +11939,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$C$2:$C$29,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$C$2:$C$30,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$C$2:$C$29,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$C$2:$C$30,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -11750,19 +11967,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$29,交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$29,交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$29,$A16,交易明細!$J$2:$J$29,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -18936,7 +19153,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr"/>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="20" t="n"/>
       <c r="F396" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,7 +18,7 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$59</f>
+              <f>'資金明細'!$R$2:$R$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 03:26（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 07:11（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,39 +1101,39 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -1142,15 +1142,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1165,15 +1165,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1188,15 +1188,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1211,15 +1211,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1234,61 +1234,61 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
@@ -1297,27 +1297,27 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -1331,47 +1331,70 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1553,13 +1576,13 @@
         <v>-0.003000000000000007</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.00620000000000001</v>
+        <v>-0.007923076923076934</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>34</v>
@@ -1651,7 +1674,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R59</f>
+        <f>資金明細!R60</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +1712,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$59)</f>
+        <f>MAX(資金明細!$R$2:$R$60)</f>
         <v/>
       </c>
     </row>
@@ -1708,7 +1731,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$59)</f>
+        <f>MIN(資金明細!$R$2:$R$60)</f>
         <v/>
       </c>
     </row>
@@ -1728,7 +1751,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$59)</f>
+        <f>MIN(資金明細!$X$2:$X$60)</f>
         <v/>
       </c>
     </row>
@@ -1747,7 +1770,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$59,"進場",資金明細!$N$2:$N$59,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$60,"進場",資金明細!$N$2:$N$60,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1766,7 +1789,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$59,"進場",資金明細!$N$2:$N$59,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$60,"進場",資金明細!$N$2:$N$60,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1777,7 +1800,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$59,"出場",資金明細!$N$2:$N$59,"已下單",資金明細!$K$2:$K$59,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$60,"出場",資金明細!$N$2:$N$60,"已下單",資金明細!$K$2:$K$60,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1797,7 +1820,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$59,"出場",資金明細!$N$2:$N$59,"已下單",資金明細!$K$2:$K$59,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$60,"出場",資金明細!$N$2:$N$60,"已下單",資金明細!$K$2:$K$60,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1813,7 +1836,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$59,"出場",資金明細!$N$2:$N$59,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$60,"出場",資金明細!$N$2:$N$60,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1829,7 +1852,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$59)</f>
+        <f>MAX(資金明細!$U$2:$U$60)</f>
         <v/>
       </c>
     </row>
@@ -1845,7 +1868,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$59)</f>
+        <f>MAX(資金明細!$S$2:$S$60)</f>
         <v/>
       </c>
     </row>
@@ -1856,7 +1879,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V59</f>
+        <f>B5*資金明細!V60</f>
         <v/>
       </c>
     </row>
@@ -1867,7 +1890,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>IF(資金明細!N59="已下單",資金明細!O59*交易明細!L30,0)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -1878,7 +1901,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$59)</f>
+        <f>MAX(資金明細!$Y$2:$Y$60)</f>
         <v/>
       </c>
     </row>
@@ -1900,7 +1923,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$59,MATCH(1,資金明細!$Z$2:$Z$59,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$60,MATCH(1,資金明細!$Z$2:$Z$60,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -1911,7 +1934,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$59,"進場",資金明細!$N$2:$N$59,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$60,"進場",資金明細!$N$2:$N$60,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -1976,7 +1999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z59"/>
+  <dimension ref="A1:Z60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7636,11 +7659,7 @@
         <v>0.2045065</v>
       </c>
       <c r="J59" s="20" t="n"/>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K59" s="2" t="n"/>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="19">
         <f>資金模擬!$B$5*V58</f>
@@ -7695,9 +7714,112 @@
         <v/>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>46280.25</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G60" s="20" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="H60" s="20" t="n">
+        <v>0.2217281</v>
+      </c>
+      <c r="I60" s="20" t="n">
+        <v>0.2045065</v>
+      </c>
+      <c r="J60" s="20" t="n">
+        <v>0.2045065</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L60" s="5">
+        <f>交易明細!K30</f>
+        <v/>
+      </c>
+      <c r="M60" s="19">
+        <f>M59</f>
+        <v/>
+      </c>
+      <c r="N60" s="2">
+        <f>N59</f>
+        <v/>
+      </c>
+      <c r="O60" s="19">
+        <f>O59</f>
+        <v/>
+      </c>
+      <c r="P60" s="4">
+        <f>交易明細!L30</f>
+        <v/>
+      </c>
+      <c r="Q60" s="13">
+        <f>IF(N60="已下單",O60*P60,0)</f>
+        <v/>
+      </c>
+      <c r="R60" s="13">
+        <f>R59+Q60</f>
+        <v/>
+      </c>
+      <c r="S60" s="19">
+        <f>S59-IF(N60="已下單",M60,0)</f>
+        <v/>
+      </c>
+      <c r="T60" s="19">
+        <f>R60-S60</f>
+        <v/>
+      </c>
+      <c r="U60" s="2">
+        <f>U59-IF(N60="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V60" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R60,0),MAX(V59,FLOOR(MAX(R60,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W60" s="13">
+        <f>MAX(W59,R60)</f>
+        <v/>
+      </c>
+      <c r="X60" s="4">
+        <f>IF(W60&gt;0,R60/W60-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y60" s="19">
+        <f>IF(R60&gt;0,S60*資金模擬!$B$7/R60,0)</f>
+        <v/>
+      </c>
+      <c r="Z60" s="2">
+        <f>IF(OR(Z59=1,R60&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z59"/>
-  <conditionalFormatting sqref="K2:K59">
+  <autoFilter ref="A1:Z60"/>
+  <conditionalFormatting sqref="K2:K60">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -7705,7 +7827,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N59">
+  <conditionalFormatting sqref="N2:N60">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -7713,7 +7835,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q59">
+  <conditionalFormatting sqref="Q2:Q60">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -7778,7 +7900,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 03:26（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 07:11（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -11043,14 +11165,14 @@
         <v>0.2045065</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>46280.125</v>
+        <v>46280.25</v>
       </c>
       <c r="I30" s="20" t="n">
-        <v>0.21967</v>
+        <v>0.2045065</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K30" s="5">
@@ -11061,11 +11183,7 @@
         <f>IF(C30="做多",I30/E30-1,1-I30/E30)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="4" t="n">
         <v>0.07694231827505127</v>
       </c>
@@ -11085,7 +11203,7 @@
         <v>0.02870813397129202</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.01337854787011661</v>
+        <v>0.05</v>
       </c>
       <c r="U30" s="19" t="n">
         <v>2.695897368776979</v>
@@ -19153,11 +19271,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C396" s="2" t="inlineStr"/>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="20" t="n"/>
       <c r="F396" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 07:11（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 09:33（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1113,50 +1113,50 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -1165,15 +1165,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1188,15 +1188,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1211,15 +1211,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1234,15 +1234,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1257,61 +1257,61 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
@@ -1320,27 +1320,27 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
@@ -1354,47 +1354,70 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1567,13 +1590,13 @@
         <v>-0.006000000000000009</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.6</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.003000000000000007</v>
+        <v>-0.001967741935483876</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>26</v>
@@ -7900,7 +7923,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 07:11（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 09:33（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 09:33（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 11:28（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1119,15 +1119,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1136,50 +1136,50 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -1188,15 +1188,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1211,15 +1211,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1234,15 +1234,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1257,15 +1257,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1280,61 +1280,61 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
@@ -1343,27 +1343,27 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
@@ -1377,47 +1377,70 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1785,7 +1808,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -7923,7 +7946,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 09:33（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 11:28（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -8115,7 +8138,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1M/5M/15M 依序判斷</t>
+          <t>5M/15M/30M 依序判斷</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 11:28（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 15:50（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1119,15 +1119,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1142,15 +1142,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1159,50 +1159,50 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -1211,15 +1211,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1234,15 +1234,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1257,15 +1257,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1280,15 +1280,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
@@ -1303,61 +1303,61 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
@@ -1366,27 +1366,27 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1</v>
@@ -1400,47 +1400,70 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1489,7 +1512,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>近 1 個月最佳區間：5%–6%（每筆 +0.55%）</t>
+          <t>近 1 個月最佳區間：5%–6%（每筆 +0.61%）</t>
         </is>
       </c>
     </row>
@@ -1604,13 +1627,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5625</v>
+        <v>0.5606060606060606</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.006000000000000009</v>
+        <v>-0.006151515151515162</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>31</v>
@@ -1631,13 +1654,13 @@
         <v>-0.007923076923076934</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.005470588235294119</v>
+        <v>0.006142857142857145</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>47</v>
@@ -7946,7 +7969,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 11:28（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 15:50（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 15:50（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 21:38（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1119,15 +1119,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1142,15 +1142,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1165,15 +1165,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1182,50 +1182,50 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -1234,15 +1234,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1257,15 +1257,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1280,15 +1280,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
@@ -1303,15 +1303,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
@@ -1326,61 +1326,61 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
@@ -1389,27 +1389,27 @@
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1</v>
@@ -1423,47 +1423,70 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1636,13 +1659,13 @@
         <v>-0.006151515151515162</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.001967741935483876</v>
+        <v>-0.002515151515151524</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>26</v>
@@ -1663,22 +1686,22 @@
         <v>0.006142857142857145</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.6595744680851063</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.001765957446808508</v>
+        <v>0.0006666666666666626</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.002333333333333329</v>
+        <v>0.003736842105263155</v>
       </c>
     </row>
   </sheetData>
@@ -7969,7 +7992,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 15:50（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-15 21:38（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,9 +18,9 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$60</f>
+              <f>'資金明細'!$R$2:$R$64</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-15 21:38（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-16 02:16（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -811,19 +811,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -831,35 +831,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$30,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$32,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$J$2:$J$30,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$J$2:$J$32,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$J$2:$J$30,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$J$2:$J$32,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$J$2:$J$30,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$J$2:$J$32,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$30,"&lt;&gt;未平倉",交易明細!$L$2:$L$30,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$32,"&lt;&gt;未平倉",交易明細!$L$2:$L$32,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$B$2:$B$30,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$B$2:$B$32,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -878,19 +878,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -898,35 +898,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$30,"做多",交易明細!$J$2:$J$30,"&lt;&gt;未平倉",交易明細!$L$2:$L$30,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"&lt;&gt;未平倉",交易明細!$L$2:$L$32,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$B$2:$B$30,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$B$2:$B$32,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -945,19 +945,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -965,35 +965,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$30,"做空",交易明細!$J$2:$J$30,"&lt;&gt;未平倉",交易明細!$L$2:$L$30,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"&lt;&gt;未平倉",交易明細!$L$2:$L$32,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,33 +1101,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1142,15 +1142,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1165,15 +1165,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1188,15 +1188,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1205,50 +1205,50 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
@@ -1257,15 +1257,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1280,15 +1280,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
@@ -1303,15 +1303,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
@@ -1326,15 +1326,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
@@ -1349,61 +1349,61 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
@@ -1412,27 +1412,27 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1</v>
@@ -1446,47 +1446,70 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1650,31 +1673,31 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5606060606060606</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.006151515151515162</v>
+        <v>-0.006294117647058834</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.002515151515151524</v>
+        <v>-0.001588235294117655</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.007923076923076934</v>
+        <v>-0.00814285714285715</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>35</v>
@@ -1695,13 +1718,13 @@
         <v>0.0006666666666666626</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.7</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.003736842105263155</v>
+        <v>0.004999999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1766,7 +1789,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R60</f>
+        <f>資金明細!R64</f>
         <v/>
       </c>
     </row>
@@ -1804,7 +1827,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$60)</f>
+        <f>MAX(資金明細!$R$2:$R$64)</f>
         <v/>
       </c>
     </row>
@@ -1823,7 +1846,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$60)</f>
+        <f>MIN(資金明細!$R$2:$R$64)</f>
         <v/>
       </c>
     </row>
@@ -1843,7 +1866,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$60)</f>
+        <f>MIN(資金明細!$X$2:$X$64)</f>
         <v/>
       </c>
     </row>
@@ -1862,7 +1885,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$60,"進場",資金明細!$N$2:$N$60,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$64,"進場",資金明細!$N$2:$N$64,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1881,7 +1904,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$60,"進場",資金明細!$N$2:$N$60,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$64,"進場",資金明細!$N$2:$N$64,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1892,7 +1915,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$60,"出場",資金明細!$N$2:$N$60,"已下單",資金明細!$K$2:$K$60,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$64,"出場",資金明細!$N$2:$N$64,"已下單",資金明細!$K$2:$K$64,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1903,7 +1926,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$30),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$32),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1912,7 +1935,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$60,"出場",資金明細!$N$2:$N$60,"已下單",資金明細!$K$2:$K$60,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$64,"出場",資金明細!$N$2:$N$64,"已下單",資金明細!$K$2:$K$64,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1928,7 +1951,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$60,"出場",資金明細!$N$2:$N$60,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$64,"出場",資金明細!$N$2:$N$64,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -1944,7 +1967,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$60)</f>
+        <f>MAX(資金明細!$U$2:$U$64)</f>
         <v/>
       </c>
     </row>
@@ -1960,7 +1983,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$60)</f>
+        <f>MAX(資金明細!$S$2:$S$64)</f>
         <v/>
       </c>
     </row>
@@ -1971,7 +1994,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V60</f>
+        <f>B5*資金明細!V64</f>
         <v/>
       </c>
     </row>
@@ -1993,7 +2016,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$60)</f>
+        <f>MAX(資金明細!$Y$2:$Y$64)</f>
         <v/>
       </c>
     </row>
@@ -2015,7 +2038,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$60,MATCH(1,資金明細!$Z$2:$Z$60,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$64,MATCH(1,資金明細!$Z$2:$Z$64,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -2026,7 +2049,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$60,"進場",資金明細!$N$2:$N$60,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$64,"進場",資金明細!$N$2:$N$64,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -2091,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z60"/>
+  <dimension ref="A1:Z64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7909,9 +7932,395 @@
         <v/>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>46280.91666666666</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G61" s="20" t="n">
+        <v>0.11513</v>
+      </c>
+      <c r="H61" s="20" t="n">
+        <v>0.1116761</v>
+      </c>
+      <c r="I61" s="20" t="n">
+        <v>0.1208865</v>
+      </c>
+      <c r="J61" s="20" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="19">
+        <f>資金模擬!$B$5*V60</f>
+        <v/>
+      </c>
+      <c r="N61" s="2">
+        <f>IF(Z60=1,"已停止",IF(T60&gt;=M61,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O61" s="19">
+        <f>IF(N61="已下單",M61*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P61" s="4" t="n"/>
+      <c r="Q61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="13">
+        <f>R60+Q61</f>
+        <v/>
+      </c>
+      <c r="S61" s="19">
+        <f>S60+IF(N61="已下單",M61,0)</f>
+        <v/>
+      </c>
+      <c r="T61" s="19">
+        <f>R61-S61</f>
+        <v/>
+      </c>
+      <c r="U61" s="2">
+        <f>U60+IF(N61="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V61" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R61,0),MAX(V60,FLOOR(MAX(R61,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W61" s="13">
+        <f>MAX(W60,R61)</f>
+        <v/>
+      </c>
+      <c r="X61" s="4">
+        <f>IF(W61&gt;0,R61/W61-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y61" s="19">
+        <f>IF(R61&gt;0,S61*資金模擬!$B$7/R61,0)</f>
+        <v/>
+      </c>
+      <c r="Z61" s="2">
+        <f>IF(OR(Z60=1,R61&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>46280.95833333334</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G62" s="20" t="n">
+        <v>0.11513</v>
+      </c>
+      <c r="H62" s="20" t="n">
+        <v>0.1116761</v>
+      </c>
+      <c r="I62" s="20" t="n">
+        <v>0.1208865</v>
+      </c>
+      <c r="J62" s="20" t="n">
+        <v>0.1116761</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L62" s="5">
+        <f>交易明細!K31</f>
+        <v/>
+      </c>
+      <c r="M62" s="19">
+        <f>M61</f>
+        <v/>
+      </c>
+      <c r="N62" s="2">
+        <f>N61</f>
+        <v/>
+      </c>
+      <c r="O62" s="19">
+        <f>O61</f>
+        <v/>
+      </c>
+      <c r="P62" s="4">
+        <f>交易明細!L31</f>
+        <v/>
+      </c>
+      <c r="Q62" s="13">
+        <f>IF(N62="已下單",O62*P62,0)</f>
+        <v/>
+      </c>
+      <c r="R62" s="13">
+        <f>R61+Q62</f>
+        <v/>
+      </c>
+      <c r="S62" s="19">
+        <f>S61-IF(N62="已下單",M62,0)</f>
+        <v/>
+      </c>
+      <c r="T62" s="19">
+        <f>R62-S62</f>
+        <v/>
+      </c>
+      <c r="U62" s="2">
+        <f>U61-IF(N62="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V62" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R62,0),MAX(V61,FLOOR(MAX(R62,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W62" s="13">
+        <f>MAX(W61,R62)</f>
+        <v/>
+      </c>
+      <c r="X62" s="4">
+        <f>IF(W62&gt;0,R62/W62-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y62" s="19">
+        <f>IF(R62&gt;0,S62*資金模擬!$B$7/R62,0)</f>
+        <v/>
+      </c>
+      <c r="Z62" s="2">
+        <f>IF(OR(Z61=1,R62&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>46280.95833333334</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G63" s="20" t="n">
+        <v>0.6319</v>
+      </c>
+      <c r="H63" s="20" t="n">
+        <v>0.612943</v>
+      </c>
+      <c r="I63" s="20" t="n">
+        <v>0.6634950000000001</v>
+      </c>
+      <c r="J63" s="20" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="19">
+        <f>資金模擬!$B$5*V62</f>
+        <v/>
+      </c>
+      <c r="N63" s="2">
+        <f>IF(Z62=1,"已停止",IF(T62&gt;=M63,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O63" s="19">
+        <f>IF(N63="已下單",M63*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P63" s="4" t="n"/>
+      <c r="Q63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="13">
+        <f>R62+Q63</f>
+        <v/>
+      </c>
+      <c r="S63" s="19">
+        <f>S62+IF(N63="已下單",M63,0)</f>
+        <v/>
+      </c>
+      <c r="T63" s="19">
+        <f>R63-S63</f>
+        <v/>
+      </c>
+      <c r="U63" s="2">
+        <f>U62+IF(N63="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V63" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R63,0),MAX(V62,FLOOR(MAX(R63,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W63" s="13">
+        <f>MAX(W62,R63)</f>
+        <v/>
+      </c>
+      <c r="X63" s="4">
+        <f>IF(W63&gt;0,R63/W63-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y63" s="19">
+        <f>IF(R63&gt;0,S63*資金模擬!$B$7/R63,0)</f>
+        <v/>
+      </c>
+      <c r="Z63" s="2">
+        <f>IF(OR(Z62=1,R63&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>46281.04166666666</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G64" s="20" t="n">
+        <v>0.6319</v>
+      </c>
+      <c r="H64" s="20" t="n">
+        <v>0.612943</v>
+      </c>
+      <c r="I64" s="20" t="n">
+        <v>0.6634950000000001</v>
+      </c>
+      <c r="J64" s="20" t="n">
+        <v>0.6634950000000001</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L64" s="5">
+        <f>交易明細!K32</f>
+        <v/>
+      </c>
+      <c r="M64" s="19">
+        <f>M63</f>
+        <v/>
+      </c>
+      <c r="N64" s="2">
+        <f>N63</f>
+        <v/>
+      </c>
+      <c r="O64" s="19">
+        <f>O63</f>
+        <v/>
+      </c>
+      <c r="P64" s="4">
+        <f>交易明細!L32</f>
+        <v/>
+      </c>
+      <c r="Q64" s="13">
+        <f>IF(N64="已下單",O64*P64,0)</f>
+        <v/>
+      </c>
+      <c r="R64" s="13">
+        <f>R63+Q64</f>
+        <v/>
+      </c>
+      <c r="S64" s="19">
+        <f>S63-IF(N64="已下單",M64,0)</f>
+        <v/>
+      </c>
+      <c r="T64" s="19">
+        <f>R64-S64</f>
+        <v/>
+      </c>
+      <c r="U64" s="2">
+        <f>U63-IF(N64="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V64" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R64,0),MAX(V63,FLOOR(MAX(R64,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W64" s="13">
+        <f>MAX(W63,R64)</f>
+        <v/>
+      </c>
+      <c r="X64" s="4">
+        <f>IF(W64&gt;0,R64/W64-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y64" s="19">
+        <f>IF(R64&gt;0,S64*資金模擬!$B$7/R64,0)</f>
+        <v/>
+      </c>
+      <c r="Z64" s="2">
+        <f>IF(OR(Z63=1,R64&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z60"/>
-  <conditionalFormatting sqref="K2:K60">
+  <autoFilter ref="A1:Z64"/>
+  <conditionalFormatting sqref="K2:K64">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -7919,7 +8328,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N60">
+  <conditionalFormatting sqref="N2:N64">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -7927,7 +8336,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q60">
+  <conditionalFormatting sqref="Q2:Q64">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -7992,7 +8401,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-15 21:38（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-16 02:16（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -8196,7 +8605,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$30),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$32),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8361,7 +8770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -11326,9 +11735,201 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>46280.91666666666</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>0.11513</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>0.1116761</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>0.1208865</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>46280.95833333334</v>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v>0.1116761</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K31" s="5">
+        <f>(H31-D31)*24</f>
+        <v/>
+      </c>
+      <c r="L31" s="4">
+        <f>IF(C31="做多",I31/E31-1,1-I31/E31)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="4" t="n">
+        <v>-0.02283143778645391</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>0.04590811279218091</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>-0.001651917915721945</v>
+      </c>
+      <c r="Q31" s="22" t="n">
+        <v>-13335483</v>
+      </c>
+      <c r="R31" s="22" t="n">
+        <v>3947406.29375</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="19" t="n">
+        <v>3.572201315293682</v>
+      </c>
+      <c r="V31" s="19" t="n">
+        <v>0.5984251968503946</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>0.08304667756741757</v>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>-0.06326191355744371</v>
+      </c>
+      <c r="Y31" s="4" t="n">
+        <v>0.004326499942148732</v>
+      </c>
+      <c r="Z31" s="4" t="n">
+        <v>0.01466104750439268</v>
+      </c>
+      <c r="AA31" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB31" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC31" s="4">
+        <f>(AB31+2*參數!$B$7)/(AA31+AB31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>46280.95833333334</v>
+      </c>
+      <c r="E32" s="20" t="n">
+        <v>0.6319</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v>0.612943</v>
+      </c>
+      <c r="G32" s="20" t="n">
+        <v>0.6634950000000001</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>46281.04166666666</v>
+      </c>
+      <c r="I32" s="20" t="n">
+        <v>0.6634950000000001</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="K32" s="5">
+        <f>(H32-D32)*24</f>
+        <v/>
+      </c>
+      <c r="L32" s="4">
+        <f>IF(C32="做多",I32/E32-1,1-I32/E32)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="4" t="n">
+        <v>-0.03067955207853967</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>0.04561528399298138</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>-0.001777180996011096</v>
+      </c>
+      <c r="Q32" s="22" t="n">
+        <v>-188505</v>
+      </c>
+      <c r="R32" s="22" t="n">
+        <v>3708159.2401</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>0.008229150181990774</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U32" s="19" t="n">
+        <v>2.135001569503176</v>
+      </c>
+      <c r="V32" s="19" t="n">
+        <v>0.6008869179600886</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>-0.06019576458587106</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>-0.09061097687262687</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>0.008791137050601638</v>
+      </c>
+      <c r="Z32" s="4" t="n">
+        <v>0.02126479226765776</v>
+      </c>
+      <c r="AA32" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB32" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC32" s="4">
+        <f>(AB32+2*參數!$B$7)/(AA32+AB32)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC30"/>
-  <conditionalFormatting sqref="J2:J30">
+  <autoFilter ref="A1:AC32"/>
+  <conditionalFormatting sqref="J2:J32">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -11349,7 +11950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11435,27 +12036,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -11463,19 +12064,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A2,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11486,27 +12087,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -11514,19 +12115,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A3,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11537,27 +12138,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -11565,50 +12166,50 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A4,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>VVV_USDT_PERP</t>
+          <t>PONS_USDT_PERP</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -11616,50 +12217,50 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A5,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HEMI_USDT_PERP</t>
+          <t>VVV_USDT_PERP</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -11667,50 +12268,50 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A6,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BULLA_USDT_PERP</t>
+          <t>HEMI_USDT_PERP</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -11718,50 +12319,50 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A7,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PONS_USDT_PERP</t>
+          <t>BULLA_USDT_PERP</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -11769,19 +12370,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A8,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11792,27 +12393,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -11820,19 +12421,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A9,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11843,27 +12444,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -11871,19 +12472,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A10,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11894,27 +12495,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -11922,19 +12523,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A11,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11945,27 +12546,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -11973,19 +12574,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A12,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -11996,27 +12597,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -12024,19 +12625,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A13,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12047,27 +12648,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -12075,19 +12676,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A14,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12098,27 +12699,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -12126,19 +12727,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A15,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12149,27 +12750,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$C$2:$C$30,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$C$2:$C$32,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$C$2:$C$30,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$C$2:$C$32,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -12177,24 +12778,75 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$30,交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$30,交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$30,$A16,交易明細!$J$2:$J$30,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$C$2:$C$32,"做多")</f>
+        <v/>
+      </c>
+      <c r="D17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$C$2:$C$32,"做空")</f>
+        <v/>
+      </c>
+      <c r="E17" s="2">
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"止損")</f>
+        <v/>
+      </c>
+      <c r="H17" s="4">
+        <f>IFERROR(F17/E17,0)</f>
+        <v/>
+      </c>
+      <c r="I17" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J17" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K17" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L16"/>
+  <autoFilter ref="A1:L17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-16 02:16（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-16 05:30（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,56 +1101,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1165,15 +1165,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1188,15 +1188,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1211,15 +1211,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1228,50 +1228,50 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1280,15 +1280,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
@@ -1303,15 +1303,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
@@ -1326,15 +1326,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
@@ -1349,15 +1349,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
@@ -1372,61 +1372,61 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
@@ -1435,27 +1435,27 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1</v>
@@ -1469,47 +1469,70 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1673,13 +1696,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.006294117647058834</v>
+        <v>-0.005285714285714296</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>34</v>
@@ -8401,7 +8424,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-16 02:16（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-16 05:30（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-16 05:30（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-16 08:26（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>442</v>
@@ -1119,61 +1119,61 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1188,15 +1188,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1211,15 +1211,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1234,15 +1234,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1251,50 +1251,50 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -1303,15 +1303,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
@@ -1326,15 +1326,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
@@ -1349,15 +1349,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
@@ -1372,15 +1372,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
@@ -1395,61 +1395,61 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
@@ -1458,27 +1458,27 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1</v>
@@ -1492,47 +1492,70 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -8424,7 +8447,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-16 05:30（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-16 08:26（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,8 +18,8 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$64</f>
+              <f>'資金明細'!$R$2:$R$67</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-16 08:26（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-16 14:07（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -811,19 +811,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -831,35 +831,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$32,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$34,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$J$2:$J$32,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$J$2:$J$34,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$J$2:$J$32,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$J$2:$J$34,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$J$2:$J$32,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$J$2:$J$34,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$32,"&lt;&gt;未平倉",交易明細!$L$2:$L$32,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$34,"&lt;&gt;未平倉",交易明細!$L$2:$L$34,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$B$2:$B$32,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$B$2:$B$34,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -878,19 +878,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -898,35 +898,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$32,"做多",交易明細!$J$2:$J$32,"&lt;&gt;未平倉",交易明細!$L$2:$L$32,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"&lt;&gt;未平倉",交易明細!$L$2:$L$34,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$B$2:$B$32,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$B$2:$B$34,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -945,19 +945,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -965,35 +965,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$32,"做空",交易明細!$J$2:$J$32,"&lt;&gt;未平倉",交易明細!$L$2:$L$32,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"&lt;&gt;未平倉",交易明細!$L$2:$L$34,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,33 +1101,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>442</v>
@@ -1142,61 +1142,61 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1211,15 +1211,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1234,15 +1234,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1257,15 +1257,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1274,50 +1274,50 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -1326,15 +1326,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
@@ -1349,15 +1349,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
@@ -1372,15 +1372,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
@@ -1395,15 +1395,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
@@ -1418,61 +1418,61 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
@@ -1481,27 +1481,27 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1</v>
@@ -1515,47 +1515,70 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1728,22 +1751,22 @@
         <v>-0.005285714285714296</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.001588235294117655</v>
+        <v>-0.0007142857142857212</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.00814285714285715</v>
+        <v>-0.006862068965517248</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>35</v>
@@ -1764,13 +1787,13 @@
         <v>0.0006666666666666626</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.7</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.004999999999999999</v>
+        <v>0.006142857142857143</v>
       </c>
     </row>
   </sheetData>
@@ -1835,7 +1858,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R64</f>
+        <f>資金明細!R67</f>
         <v/>
       </c>
     </row>
@@ -1873,7 +1896,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$64)</f>
+        <f>MAX(資金明細!$R$2:$R$67)</f>
         <v/>
       </c>
     </row>
@@ -1892,7 +1915,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$64)</f>
+        <f>MIN(資金明細!$R$2:$R$67)</f>
         <v/>
       </c>
     </row>
@@ -1912,7 +1935,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$64)</f>
+        <f>MIN(資金明細!$X$2:$X$67)</f>
         <v/>
       </c>
     </row>
@@ -1931,7 +1954,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$64,"進場",資金明細!$N$2:$N$64,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$67,"進場",資金明細!$N$2:$N$67,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1950,7 +1973,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$64,"進場",資金明細!$N$2:$N$64,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$67,"進場",資金明細!$N$2:$N$67,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1961,7 +1984,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$64,"出場",資金明細!$N$2:$N$64,"已下單",資金明細!$K$2:$K$64,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$67,"出場",資金明細!$N$2:$N$67,"已下單",資金明細!$K$2:$K$67,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -1972,7 +1995,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$32),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$34),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1981,7 +2004,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$64,"出場",資金明細!$N$2:$N$64,"已下單",資金明細!$K$2:$K$64,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$67,"出場",資金明細!$N$2:$N$67,"已下單",資金明細!$K$2:$K$67,"止損")</f>
         <v/>
       </c>
     </row>
@@ -1997,7 +2020,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$64,"出場",資金明細!$N$2:$N$64,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$67,"出場",資金明細!$N$2:$N$67,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -2013,7 +2036,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$64)</f>
+        <f>MAX(資金明細!$U$2:$U$67)</f>
         <v/>
       </c>
     </row>
@@ -2029,7 +2052,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$64)</f>
+        <f>MAX(資金明細!$S$2:$S$67)</f>
         <v/>
       </c>
     </row>
@@ -2040,7 +2063,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V64</f>
+        <f>B5*資金明細!V67</f>
         <v/>
       </c>
     </row>
@@ -2051,7 +2074,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>0</f>
+        <f>IF(資金明細!N66="已下單",資金明細!O66*交易明細!L34,0)</f>
         <v/>
       </c>
     </row>
@@ -2062,7 +2085,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$64)</f>
+        <f>MAX(資金明細!$Y$2:$Y$67)</f>
         <v/>
       </c>
     </row>
@@ -2084,7 +2107,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$64,MATCH(1,資金明細!$Z$2:$Z$64,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$67,MATCH(1,資金明細!$Z$2:$Z$67,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -2095,7 +2118,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$64,"進場",資金明細!$N$2:$N$64,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$67,"進場",資金明細!$N$2:$N$67,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -2160,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z64"/>
+  <dimension ref="A1:Z67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8364,9 +8387,296 @@
         <v/>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>46281.41666666666</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G65" s="20" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="H65" s="20" t="n">
+        <v>0.5910209999999999</v>
+      </c>
+      <c r="I65" s="20" t="n">
+        <v>0.639765</v>
+      </c>
+      <c r="J65" s="20" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="19">
+        <f>資金模擬!$B$5*V64</f>
+        <v/>
+      </c>
+      <c r="N65" s="2">
+        <f>IF(Z64=1,"已停止",IF(T64&gt;=M65,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O65" s="19">
+        <f>IF(N65="已下單",M65*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P65" s="4" t="n"/>
+      <c r="Q65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="13">
+        <f>R64+Q65</f>
+        <v/>
+      </c>
+      <c r="S65" s="19">
+        <f>S64+IF(N65="已下單",M65,0)</f>
+        <v/>
+      </c>
+      <c r="T65" s="19">
+        <f>R65-S65</f>
+        <v/>
+      </c>
+      <c r="U65" s="2">
+        <f>U64+IF(N65="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V65" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R65,0),MAX(V64,FLOOR(MAX(R65,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W65" s="13">
+        <f>MAX(W64,R65)</f>
+        <v/>
+      </c>
+      <c r="X65" s="4">
+        <f>IF(W65&gt;0,R65/W65-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y65" s="19">
+        <f>IF(R65&gt;0,S65*資金模擬!$B$7/R65,0)</f>
+        <v/>
+      </c>
+      <c r="Z65" s="2">
+        <f>IF(OR(Z64=1,R65&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>46281.41666666666</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G66" s="20" t="n">
+        <v>0.11407</v>
+      </c>
+      <c r="H66" s="20" t="n">
+        <v>0.1106479</v>
+      </c>
+      <c r="I66" s="20" t="n">
+        <v>0.1197735</v>
+      </c>
+      <c r="J66" s="20" t="n"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="19">
+        <f>資金模擬!$B$5*V65</f>
+        <v/>
+      </c>
+      <c r="N66" s="2">
+        <f>IF(Z65=1,"已停止",IF(T65&gt;=M66,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O66" s="19">
+        <f>IF(N66="已下單",M66*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P66" s="4" t="n"/>
+      <c r="Q66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="13">
+        <f>R65+Q66</f>
+        <v/>
+      </c>
+      <c r="S66" s="19">
+        <f>S65+IF(N66="已下單",M66,0)</f>
+        <v/>
+      </c>
+      <c r="T66" s="19">
+        <f>R66-S66</f>
+        <v/>
+      </c>
+      <c r="U66" s="2">
+        <f>U65+IF(N66="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V66" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R66,0),MAX(V65,FLOOR(MAX(R66,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W66" s="13">
+        <f>MAX(W65,R66)</f>
+        <v/>
+      </c>
+      <c r="X66" s="4">
+        <f>IF(W66&gt;0,R66/W66-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y66" s="19">
+        <f>IF(R66&gt;0,S66*資金模擬!$B$7/R66,0)</f>
+        <v/>
+      </c>
+      <c r="Z66" s="2">
+        <f>IF(OR(Z65=1,R66&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>46281.5</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G67" s="20" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="H67" s="20" t="n">
+        <v>0.5910209999999999</v>
+      </c>
+      <c r="I67" s="20" t="n">
+        <v>0.639765</v>
+      </c>
+      <c r="J67" s="20" t="n">
+        <v>0.5910209999999999</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L67" s="5">
+        <f>交易明細!K33</f>
+        <v/>
+      </c>
+      <c r="M67" s="19">
+        <f>M65</f>
+        <v/>
+      </c>
+      <c r="N67" s="2">
+        <f>N65</f>
+        <v/>
+      </c>
+      <c r="O67" s="19">
+        <f>O65</f>
+        <v/>
+      </c>
+      <c r="P67" s="4">
+        <f>交易明細!L33</f>
+        <v/>
+      </c>
+      <c r="Q67" s="13">
+        <f>IF(N67="已下單",O67*P67,0)</f>
+        <v/>
+      </c>
+      <c r="R67" s="13">
+        <f>R66+Q67</f>
+        <v/>
+      </c>
+      <c r="S67" s="19">
+        <f>S66-IF(N67="已下單",M67,0)</f>
+        <v/>
+      </c>
+      <c r="T67" s="19">
+        <f>R67-S67</f>
+        <v/>
+      </c>
+      <c r="U67" s="2">
+        <f>U66-IF(N67="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V67" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R67,0),MAX(V66,FLOOR(MAX(R67,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W67" s="13">
+        <f>MAX(W66,R67)</f>
+        <v/>
+      </c>
+      <c r="X67" s="4">
+        <f>IF(W67&gt;0,R67/W67-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y67" s="19">
+        <f>IF(R67&gt;0,S67*資金模擬!$B$7/R67,0)</f>
+        <v/>
+      </c>
+      <c r="Z67" s="2">
+        <f>IF(OR(Z66=1,R67&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z64"/>
-  <conditionalFormatting sqref="K2:K64">
+  <autoFilter ref="A1:Z67"/>
+  <conditionalFormatting sqref="K2:K67">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -8374,7 +8684,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N64">
+  <conditionalFormatting sqref="N2:N67">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -8382,7 +8692,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q64">
+  <conditionalFormatting sqref="Q2:Q67">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -8447,7 +8757,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-16 08:26（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-16 14:07（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -8651,7 +8961,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$32),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$34),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8816,7 +9126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -11973,9 +12283,205 @@
         <v/>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PONS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>46281.41666666666</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>0.5910209999999999</v>
+      </c>
+      <c r="G33" s="20" t="n">
+        <v>0.639765</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>46281.5</v>
+      </c>
+      <c r="I33" s="20" t="n">
+        <v>0.5910209999999999</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K33" s="5">
+        <f>(H33-D33)*24</f>
+        <v/>
+      </c>
+      <c r="L33" s="4">
+        <f>IF(C33="做多",I33/E33-1,1-I33/E33)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="4" t="n">
+        <v>-0.0371365360303415</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>0.04503466628165607</v>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>-0.04653109767070673</v>
+      </c>
+      <c r="Q33" s="22" t="n">
+        <v>-522329</v>
+      </c>
+      <c r="R33" s="22" t="n">
+        <v>3799658.9706</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>0.008042015427539795</v>
+      </c>
+      <c r="U33" s="19" t="n">
+        <v>0.4664810909990809</v>
+      </c>
+      <c r="V33" s="19" t="n">
+        <v>0.9928571428571437</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>-0.01623507670548352</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>0.02433947157726202</v>
+      </c>
+      <c r="Y33" s="4" t="n">
+        <v>0.003551905352945806</v>
+      </c>
+      <c r="Z33" s="4" t="n">
+        <v>0.01159420365782837</v>
+      </c>
+      <c r="AA33" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB33" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC33" s="4">
+        <f>(AB33+2*參數!$B$7)/(AA33+AB33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>46281.41666666666</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>0.11407</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>0.1106479</v>
+      </c>
+      <c r="G34" s="20" t="n">
+        <v>0.1197735</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>46281.58333333334</v>
+      </c>
+      <c r="I34" s="20" t="n">
+        <v>0.11252</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K34" s="5">
+        <f>(H34-D34)*24</f>
+        <v/>
+      </c>
+      <c r="L34" s="4">
+        <f>IF(C34="做多",I34/E34-1,1-I34/E34)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>-0.02245265232667748</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>0.04160649993392866</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>-0.007011939012234847</v>
+      </c>
+      <c r="Q34" s="22" t="n">
+        <v>-6985142</v>
+      </c>
+      <c r="R34" s="22" t="n">
+        <v>2887294.37661</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>0.01656877356009467</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>0.01981239589725603</v>
+      </c>
+      <c r="U34" s="19" t="n">
+        <v>0.7082025381006778</v>
+      </c>
+      <c r="V34" s="19" t="n">
+        <v>0.8578553615960097</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>0.07673455248295025</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>0.04479986601909225</v>
+      </c>
+      <c r="Y34" s="4" t="n">
+        <v>0.003551905352945806</v>
+      </c>
+      <c r="Z34" s="4" t="n">
+        <v>0.01159420365782837</v>
+      </c>
+      <c r="AA34" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB34" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC34" s="4">
+        <f>(AB34+2*參數!$B$7)/(AA34+AB34)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC32"/>
-  <conditionalFormatting sqref="J2:J32">
+  <autoFilter ref="A1:AC34"/>
+  <conditionalFormatting sqref="J2:J34">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -12082,27 +12588,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -12110,50 +12616,50 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A2,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>USELESS_USDT_PERP</t>
+          <t>PONS_USDT_PERP</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -12161,50 +12667,50 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A3,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>UAI_USDT_PERP</t>
+          <t>USELESS_USDT_PERP</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -12212,50 +12718,50 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A4,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PONS_USDT_PERP</t>
+          <t>UAI_USDT_PERP</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -12263,19 +12769,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A5,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12286,27 +12792,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -12314,19 +12820,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A6,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12337,27 +12843,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -12365,19 +12871,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A7,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12388,27 +12894,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -12416,19 +12922,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A8,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12439,27 +12945,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -12467,50 +12973,50 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A9,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ACE_USDT_PERP</t>
+          <t>牛来_USDT_PERP</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -12518,50 +13024,50 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A10,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ARB_USDT_PERP</t>
+          <t>ACE_USDT_PERP</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -12569,50 +13075,50 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A11,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DASH_USDT_PERP</t>
+          <t>ARB_USDT_PERP</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -12620,50 +13126,50 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A12,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>IOST_USDT_PERP</t>
+          <t>DASH_USDT_PERP</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -12671,50 +13177,50 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A13,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CASHCAT_USDT_PERP</t>
+          <t>IOST_USDT_PERP</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -12722,50 +13228,50 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A14,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AKE_USDT_PERP</t>
+          <t>CASHCAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -12773,50 +13279,50 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A15,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LAB_USDT_PERP</t>
+          <t>AKE_USDT_PERP</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -12824,50 +13330,50 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A16,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>牛来_USDT_PERP</t>
+          <t>LAB_USDT_PERP</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$C$2:$C$32,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$C$2:$C$34,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$C$2:$C$32,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$C$2:$C$34,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -12875,19 +13381,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$32,交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$32,交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$32,$A17,交易明細!$J$2:$J$32,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -20907,7 +21413,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr"/>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="20" t="n"/>
       <c r="F443" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,7 +18,7 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$67</f>
+              <f>'資金明細'!$R$2:$R$68</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-16 14:07（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-16 19:45（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,16 +1101,16 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -1119,38 +1119,38 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>442</v>
@@ -1165,61 +1165,61 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1234,15 +1234,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1257,15 +1257,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1280,15 +1280,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
@@ -1297,50 +1297,50 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -1349,15 +1349,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
@@ -1372,15 +1372,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
@@ -1395,15 +1395,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
@@ -1418,15 +1418,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
@@ -1441,61 +1441,61 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
@@ -1504,27 +1504,27 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1</v>
@@ -1538,47 +1538,70 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1742,13 +1765,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.005285714285714296</v>
+        <v>-0.006555555555555568</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>35</v>
@@ -1760,13 +1783,13 @@
         <v>-0.0007142857142857212</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.006862068965517248</v>
+        <v>-0.005666666666666671</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>35</v>
@@ -1778,13 +1801,13 @@
         <v>0.006142857142857145</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.0006666666666666626</v>
+        <v>-0.0003877551020408212</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>21</v>
@@ -1858,7 +1881,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R67</f>
+        <f>資金明細!R68</f>
         <v/>
       </c>
     </row>
@@ -1896,7 +1919,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$67)</f>
+        <f>MAX(資金明細!$R$2:$R$68)</f>
         <v/>
       </c>
     </row>
@@ -1915,7 +1938,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$67)</f>
+        <f>MIN(資金明細!$R$2:$R$68)</f>
         <v/>
       </c>
     </row>
@@ -1935,7 +1958,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$67)</f>
+        <f>MIN(資金明細!$X$2:$X$68)</f>
         <v/>
       </c>
     </row>
@@ -1954,7 +1977,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$67,"進場",資金明細!$N$2:$N$67,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$68,"進場",資金明細!$N$2:$N$68,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1973,7 +1996,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$67,"進場",資金明細!$N$2:$N$67,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$68,"進場",資金明細!$N$2:$N$68,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -1984,7 +2007,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$67,"出場",資金明細!$N$2:$N$67,"已下單",資金明細!$K$2:$K$67,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$68,"出場",資金明細!$N$2:$N$68,"已下單",資金明細!$K$2:$K$68,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -2004,7 +2027,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$67,"出場",資金明細!$N$2:$N$67,"已下單",資金明細!$K$2:$K$67,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$68,"出場",資金明細!$N$2:$N$68,"已下單",資金明細!$K$2:$K$68,"止損")</f>
         <v/>
       </c>
     </row>
@@ -2020,7 +2043,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$67,"出場",資金明細!$N$2:$N$67,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$68,"出場",資金明細!$N$2:$N$68,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -2036,7 +2059,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$67)</f>
+        <f>MAX(資金明細!$U$2:$U$68)</f>
         <v/>
       </c>
     </row>
@@ -2052,7 +2075,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$67)</f>
+        <f>MAX(資金明細!$S$2:$S$68)</f>
         <v/>
       </c>
     </row>
@@ -2063,7 +2086,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V67</f>
+        <f>B5*資金明細!V68</f>
         <v/>
       </c>
     </row>
@@ -2074,7 +2097,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>IF(資金明細!N66="已下單",資金明細!O66*交易明細!L34,0)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -2085,7 +2108,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$67)</f>
+        <f>MAX(資金明細!$Y$2:$Y$68)</f>
         <v/>
       </c>
     </row>
@@ -2107,7 +2130,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$67,MATCH(1,資金明細!$Z$2:$Z$67,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$68,MATCH(1,資金明細!$Z$2:$Z$68,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -2118,7 +2141,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$67,"進場",資金明細!$N$2:$N$67,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$68,"進場",資金明細!$N$2:$N$68,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -2183,7 +2206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z67"/>
+  <dimension ref="A1:Z68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8512,11 +8535,7 @@
         <v>0.1197735</v>
       </c>
       <c r="J66" s="20" t="n"/>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K66" s="2" t="n"/>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="19">
         <f>資金模擬!$B$5*V65</f>
@@ -8674,9 +8693,112 @@
         <v/>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>46281.70833333334</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G68" s="20" t="n">
+        <v>0.11407</v>
+      </c>
+      <c r="H68" s="20" t="n">
+        <v>0.1106479</v>
+      </c>
+      <c r="I68" s="20" t="n">
+        <v>0.1197735</v>
+      </c>
+      <c r="J68" s="20" t="n">
+        <v>0.1106479</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L68" s="5">
+        <f>交易明細!K34</f>
+        <v/>
+      </c>
+      <c r="M68" s="19">
+        <f>M66</f>
+        <v/>
+      </c>
+      <c r="N68" s="2">
+        <f>N66</f>
+        <v/>
+      </c>
+      <c r="O68" s="19">
+        <f>O66</f>
+        <v/>
+      </c>
+      <c r="P68" s="4">
+        <f>交易明細!L34</f>
+        <v/>
+      </c>
+      <c r="Q68" s="13">
+        <f>IF(N68="已下單",O68*P68,0)</f>
+        <v/>
+      </c>
+      <c r="R68" s="13">
+        <f>R67+Q68</f>
+        <v/>
+      </c>
+      <c r="S68" s="19">
+        <f>S67-IF(N68="已下單",M68,0)</f>
+        <v/>
+      </c>
+      <c r="T68" s="19">
+        <f>R68-S68</f>
+        <v/>
+      </c>
+      <c r="U68" s="2">
+        <f>U67-IF(N68="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V68" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R68,0),MAX(V67,FLOOR(MAX(R68,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W68" s="13">
+        <f>MAX(W67,R68)</f>
+        <v/>
+      </c>
+      <c r="X68" s="4">
+        <f>IF(W68&gt;0,R68/W68-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y68" s="19">
+        <f>IF(R68&gt;0,S68*資金模擬!$B$7/R68,0)</f>
+        <v/>
+      </c>
+      <c r="Z68" s="2">
+        <f>IF(OR(Z67=1,R68&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z67"/>
-  <conditionalFormatting sqref="K2:K67">
+  <autoFilter ref="A1:Z68"/>
+  <conditionalFormatting sqref="K2:K68">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -8684,7 +8806,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N67">
+  <conditionalFormatting sqref="N2:N68">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -8692,7 +8814,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q67">
+  <conditionalFormatting sqref="Q2:Q68">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -8757,7 +8879,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-16 14:07（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-16 19:45（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -12406,14 +12528,14 @@
         <v>0.1197735</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>46281.58333333334</v>
+        <v>46281.70833333334</v>
       </c>
       <c r="I34" s="20" t="n">
-        <v>0.11252</v>
+        <v>0.1106479</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K34" s="5">
@@ -12424,11 +12546,7 @@
         <f>IF(C34="做多",I34/E34-1,1-I34/E34)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="4" t="n">
         <v>-0.02245265232667748</v>
       </c>
@@ -12445,7 +12563,7 @@
         <v>2887294.37661</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.01656877356009467</v>
+        <v>0.03</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.01981239589725603</v>
@@ -21413,11 +21531,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C443" s="2" t="inlineStr"/>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="20" t="n"/>
       <c r="F443" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,8 +18,8 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$68</f>
+              <f>'資金明細'!$R$2:$R$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-16 19:45（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 01:05（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -811,19 +811,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -831,35 +831,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$34,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$35,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$J$2:$J$34,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$J$2:$J$35,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$J$2:$J$34,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$J$2:$J$35,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$J$2:$J$34,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$J$2:$J$35,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$34,"&lt;&gt;未平倉",交易明細!$L$2:$L$34,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$35,"&lt;&gt;未平倉",交易明細!$L$2:$L$35,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$B$2:$B$34,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$B$2:$B$35,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -878,19 +878,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -898,35 +898,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$34,"做多",交易明細!$J$2:$J$34,"&lt;&gt;未平倉",交易明細!$L$2:$L$34,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"&lt;&gt;未平倉",交易明細!$L$2:$L$35,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$B$2:$B$34,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$B$2:$B$35,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -945,19 +945,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -965,35 +965,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$34,"做空",交易明細!$J$2:$J$34,"&lt;&gt;未平倉",交易明細!$L$2:$L$34,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"&lt;&gt;未平倉",交易明細!$L$2:$L$35,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,39 +1101,39 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -1142,38 +1142,38 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>442</v>
@@ -1188,61 +1188,61 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1257,15 +1257,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1280,15 +1280,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
@@ -1303,15 +1303,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
@@ -1320,50 +1320,50 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -1372,15 +1372,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
@@ -1395,15 +1395,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
@@ -1418,15 +1418,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
@@ -1441,15 +1441,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
@@ -1464,61 +1464,61 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
@@ -1527,27 +1527,27 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1</v>
@@ -1561,47 +1561,70 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1765,22 +1788,22 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5675675675675675</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.006555555555555568</v>
+        <v>-0.005594594594594606</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.0007142857142857212</v>
+        <v>0.000111111111111105</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
@@ -1801,13 +1824,13 @@
         <v>0.006142857142857145</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.6326530612244898</v>
+        <v>0.62</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.0003877551020408212</v>
+        <v>-0.001400000000000006</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>21</v>
@@ -1881,7 +1904,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R68</f>
+        <f>資金明細!R69</f>
         <v/>
       </c>
     </row>
@@ -1919,7 +1942,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$68)</f>
+        <f>MAX(資金明細!$R$2:$R$69)</f>
         <v/>
       </c>
     </row>
@@ -1938,7 +1961,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$68)</f>
+        <f>MIN(資金明細!$R$2:$R$69)</f>
         <v/>
       </c>
     </row>
@@ -1958,7 +1981,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$68)</f>
+        <f>MIN(資金明細!$X$2:$X$69)</f>
         <v/>
       </c>
     </row>
@@ -1977,7 +2000,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$68,"進場",資金明細!$N$2:$N$68,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$69,"進場",資金明細!$N$2:$N$69,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -1996,7 +2019,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$68,"進場",資金明細!$N$2:$N$68,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$69,"進場",資金明細!$N$2:$N$69,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -2007,7 +2030,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$68,"出場",資金明細!$N$2:$N$68,"已下單",資金明細!$K$2:$K$68,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$69,"出場",資金明細!$N$2:$N$69,"已下單",資金明細!$K$2:$K$69,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -2018,7 +2041,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$34),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$35),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2027,7 +2050,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$68,"出場",資金明細!$N$2:$N$68,"已下單",資金明細!$K$2:$K$68,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$69,"出場",資金明細!$N$2:$N$69,"已下單",資金明細!$K$2:$K$69,"止損")</f>
         <v/>
       </c>
     </row>
@@ -2043,7 +2066,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$68,"出場",資金明細!$N$2:$N$68,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$69,"出場",資金明細!$N$2:$N$69,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -2059,7 +2082,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$68)</f>
+        <f>MAX(資金明細!$U$2:$U$69)</f>
         <v/>
       </c>
     </row>
@@ -2075,7 +2098,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$68)</f>
+        <f>MAX(資金明細!$S$2:$S$69)</f>
         <v/>
       </c>
     </row>
@@ -2086,7 +2109,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V68</f>
+        <f>B5*資金明細!V69</f>
         <v/>
       </c>
     </row>
@@ -2097,7 +2120,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>0</f>
+        <f>IF(資金明細!N69="已下單",資金明細!O69*交易明細!L35,0)</f>
         <v/>
       </c>
     </row>
@@ -2108,7 +2131,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$68)</f>
+        <f>MAX(資金明細!$Y$2:$Y$69)</f>
         <v/>
       </c>
     </row>
@@ -2130,7 +2153,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$68,MATCH(1,資金明細!$Z$2:$Z$68,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$69,MATCH(1,資金明細!$Z$2:$Z$69,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -2141,7 +2164,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$68,"進場",資金明細!$N$2:$N$68,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$69,"進場",資金明細!$N$2:$N$69,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -2206,7 +2229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z68"/>
+  <dimension ref="A1:Z69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8796,9 +8819,103 @@
         <v/>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G69" s="20" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="H69" s="20" t="n">
+        <v>0.21825</v>
+      </c>
+      <c r="I69" s="20" t="n">
+        <v>0.23625</v>
+      </c>
+      <c r="J69" s="20" t="n"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="19">
+        <f>資金模擬!$B$5*V68</f>
+        <v/>
+      </c>
+      <c r="N69" s="2">
+        <f>IF(Z68=1,"已停止",IF(T68&gt;=M69,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O69" s="19">
+        <f>IF(N69="已下單",M69*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P69" s="4" t="n"/>
+      <c r="Q69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="13">
+        <f>R68+Q69</f>
+        <v/>
+      </c>
+      <c r="S69" s="19">
+        <f>S68+IF(N69="已下單",M69,0)</f>
+        <v/>
+      </c>
+      <c r="T69" s="19">
+        <f>R69-S69</f>
+        <v/>
+      </c>
+      <c r="U69" s="2">
+        <f>U68+IF(N69="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V69" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R69,0),MAX(V68,FLOOR(MAX(R69,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W69" s="13">
+        <f>MAX(W68,R69)</f>
+        <v/>
+      </c>
+      <c r="X69" s="4">
+        <f>IF(W69&gt;0,R69/W69-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y69" s="19">
+        <f>IF(R69&gt;0,S69*資金模擬!$B$7/R69,0)</f>
+        <v/>
+      </c>
+      <c r="Z69" s="2">
+        <f>IF(OR(Z68=1,R69&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z68"/>
-  <conditionalFormatting sqref="K2:K68">
+  <autoFilter ref="A1:Z69"/>
+  <conditionalFormatting sqref="K2:K69">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -8806,7 +8923,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N68">
+  <conditionalFormatting sqref="N2:N69">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -8814,7 +8931,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q68">
+  <conditionalFormatting sqref="Q2:Q69">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -8879,7 +8996,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-16 19:45（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-17 01:05（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9083,7 +9200,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$34),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$35),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -9248,7 +9365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -12597,9 +12714,109 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="F35" s="20" t="n">
+        <v>0.21825</v>
+      </c>
+      <c r="G35" s="20" t="n">
+        <v>0.23625</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>46282.04166666666</v>
+      </c>
+      <c r="I35" s="20" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K35" s="5">
+        <f>(H35-D35)*24</f>
+        <v/>
+      </c>
+      <c r="L35" s="4">
+        <f>IF(C35="做多",I35/E35-1,1-I35/E35)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>-0.03292357947219116</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>0.04095456277656997</v>
+      </c>
+      <c r="P35" s="4" t="n">
+        <v>-0.0164514881088984</v>
+      </c>
+      <c r="Q35" s="22" t="n">
+        <v>-778608</v>
+      </c>
+      <c r="R35" s="22" t="n">
+        <v>2914314.34629</v>
+      </c>
+      <c r="S35" s="4" t="n">
+        <v>0.005422222222222217</v>
+      </c>
+      <c r="T35" s="4" t="n">
+        <v>0.02377777777777768</v>
+      </c>
+      <c r="U35" s="19" t="n">
+        <v>1.22830388521858</v>
+      </c>
+      <c r="V35" s="19" t="n">
+        <v>0.881369426751591</v>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>-0.03547633982584686</v>
+      </c>
+      <c r="X35" s="4" t="n">
+        <v>-0.101213782302271</v>
+      </c>
+      <c r="Y35" s="4" t="n">
+        <v>-0.001227850125626873</v>
+      </c>
+      <c r="Z35" s="4" t="n">
+        <v>0.0003683615984713118</v>
+      </c>
+      <c r="AA35" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB35" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC35" s="4">
+        <f>(AB35+2*參數!$B$7)/(AA35+AB35)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC34"/>
-  <conditionalFormatting sqref="J2:J34">
+  <autoFilter ref="A1:AC35"/>
+  <conditionalFormatting sqref="J2:J35">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -12706,27 +12923,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -12734,50 +12951,50 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A2,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PONS_USDT_PERP</t>
+          <t>USELESS_USDT_PERP</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -12785,50 +13002,50 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A3,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>USELESS_USDT_PERP</t>
+          <t>PONS_USDT_PERP</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -12836,19 +13053,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A4,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12859,27 +13076,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -12887,19 +13104,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A5,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12910,27 +13127,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -12938,19 +13155,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A6,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12961,27 +13178,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -12989,19 +13206,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A7,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13012,27 +13229,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -13040,19 +13257,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A8,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13063,27 +13280,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -13091,19 +13308,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A9,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13114,27 +13331,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -13142,19 +13359,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A10,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13165,27 +13382,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -13193,19 +13410,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A11,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13216,27 +13433,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -13244,19 +13461,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A12,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13267,27 +13484,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -13295,19 +13512,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A13,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13318,27 +13535,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -13346,19 +13563,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A14,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13369,27 +13586,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -13397,19 +13614,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A15,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13420,27 +13637,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -13448,19 +13665,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A16,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13471,27 +13688,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$C$2:$C$34,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$C$2:$C$35,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$C$2:$C$34,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$C$2:$C$35,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -13499,19 +13716,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$34,交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$34,交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$34,$A17,交易明細!$J$2:$J$34,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -20685,7 +20902,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr"/>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="20" t="n"/>
       <c r="F396" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,7 +18,7 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$69</f>
+              <f>'資金明細'!$R$2:$R$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 01:05（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 04:13（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,62 +1101,62 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -1165,38 +1165,38 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>442</v>
@@ -1211,61 +1211,61 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1280,15 +1280,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
@@ -1303,15 +1303,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
@@ -1326,15 +1326,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
@@ -1343,50 +1343,50 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
@@ -1395,15 +1395,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
@@ -1418,15 +1418,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
@@ -1441,15 +1441,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
@@ -1464,15 +1464,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
@@ -1487,61 +1487,61 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
@@ -1550,27 +1550,27 @@
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1</v>
@@ -1584,47 +1584,70 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1806,13 +1829,13 @@
         <v>0.000111111111111105</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.005666666666666671</v>
+        <v>-0.007129032258064522</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>35</v>
@@ -1904,7 +1927,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R69</f>
+        <f>資金明細!R70</f>
         <v/>
       </c>
     </row>
@@ -1942,7 +1965,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$69)</f>
+        <f>MAX(資金明細!$R$2:$R$70)</f>
         <v/>
       </c>
     </row>
@@ -1961,7 +1984,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$69)</f>
+        <f>MIN(資金明細!$R$2:$R$70)</f>
         <v/>
       </c>
     </row>
@@ -1981,7 +2004,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$69)</f>
+        <f>MIN(資金明細!$X$2:$X$70)</f>
         <v/>
       </c>
     </row>
@@ -2000,7 +2023,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$69,"進場",資金明細!$N$2:$N$69,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$70,"進場",資金明細!$N$2:$N$70,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -2019,7 +2042,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$69,"進場",資金明細!$N$2:$N$69,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$70,"進場",資金明細!$N$2:$N$70,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -2030,7 +2053,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$69,"出場",資金明細!$N$2:$N$69,"已下單",資金明細!$K$2:$K$69,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$70,"出場",資金明細!$N$2:$N$70,"已下單",資金明細!$K$2:$K$70,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -2050,7 +2073,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$69,"出場",資金明細!$N$2:$N$69,"已下單",資金明細!$K$2:$K$69,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$70,"出場",資金明細!$N$2:$N$70,"已下單",資金明細!$K$2:$K$70,"止損")</f>
         <v/>
       </c>
     </row>
@@ -2066,7 +2089,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$69,"出場",資金明細!$N$2:$N$69,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$70,"出場",資金明細!$N$2:$N$70,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -2082,7 +2105,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$69)</f>
+        <f>MAX(資金明細!$U$2:$U$70)</f>
         <v/>
       </c>
     </row>
@@ -2098,7 +2121,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$69)</f>
+        <f>MAX(資金明細!$S$2:$S$70)</f>
         <v/>
       </c>
     </row>
@@ -2109,7 +2132,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V69</f>
+        <f>B5*資金明細!V70</f>
         <v/>
       </c>
     </row>
@@ -2120,7 +2143,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>IF(資金明細!N69="已下單",資金明細!O69*交易明細!L35,0)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -2131,7 +2154,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$69)</f>
+        <f>MAX(資金明細!$Y$2:$Y$70)</f>
         <v/>
       </c>
     </row>
@@ -2153,7 +2176,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$69,MATCH(1,資金明細!$Z$2:$Z$69,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$70,MATCH(1,資金明細!$Z$2:$Z$70,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -2164,7 +2187,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$69,"進場",資金明細!$N$2:$N$69,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$70,"進場",資金明細!$N$2:$N$70,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -2229,7 +2252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z69"/>
+  <dimension ref="A1:Z70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8854,11 +8877,7 @@
         <v>0.23625</v>
       </c>
       <c r="J69" s="20" t="n"/>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K69" s="2" t="n"/>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="19">
         <f>資金模擬!$B$5*V68</f>
@@ -8913,9 +8932,112 @@
         <v/>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>46282.125</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G70" s="20" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="H70" s="20" t="n">
+        <v>0.21825</v>
+      </c>
+      <c r="I70" s="20" t="n">
+        <v>0.23625</v>
+      </c>
+      <c r="J70" s="20" t="n">
+        <v>0.23625</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L70" s="5">
+        <f>交易明細!K35</f>
+        <v/>
+      </c>
+      <c r="M70" s="19">
+        <f>M69</f>
+        <v/>
+      </c>
+      <c r="N70" s="2">
+        <f>N69</f>
+        <v/>
+      </c>
+      <c r="O70" s="19">
+        <f>O69</f>
+        <v/>
+      </c>
+      <c r="P70" s="4">
+        <f>交易明細!L35</f>
+        <v/>
+      </c>
+      <c r="Q70" s="13">
+        <f>IF(N70="已下單",O70*P70,0)</f>
+        <v/>
+      </c>
+      <c r="R70" s="13">
+        <f>R69+Q70</f>
+        <v/>
+      </c>
+      <c r="S70" s="19">
+        <f>S69-IF(N70="已下單",M70,0)</f>
+        <v/>
+      </c>
+      <c r="T70" s="19">
+        <f>R70-S70</f>
+        <v/>
+      </c>
+      <c r="U70" s="2">
+        <f>U69-IF(N70="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V70" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R70,0),MAX(V69,FLOOR(MAX(R70,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W70" s="13">
+        <f>MAX(W69,R70)</f>
+        <v/>
+      </c>
+      <c r="X70" s="4">
+        <f>IF(W70&gt;0,R70/W70-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y70" s="19">
+        <f>IF(R70&gt;0,S70*資金模擬!$B$7/R70,0)</f>
+        <v/>
+      </c>
+      <c r="Z70" s="2">
+        <f>IF(OR(Z69=1,R70&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z69"/>
-  <conditionalFormatting sqref="K2:K69">
+  <autoFilter ref="A1:Z70"/>
+  <conditionalFormatting sqref="K2:K70">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -8923,7 +9045,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N69">
+  <conditionalFormatting sqref="N2:N70">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -8931,7 +9053,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q69">
+  <conditionalFormatting sqref="Q2:Q70">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -8996,7 +9118,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-17 01:05（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-17 04:13（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -12741,14 +12863,14 @@
         <v>0.23625</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>46282.04166666666</v>
+        <v>46282.125</v>
       </c>
       <c r="I35" s="20" t="n">
-        <v>0.2279</v>
+        <v>0.23625</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K35" s="5">
@@ -12759,11 +12881,7 @@
         <f>IF(C35="做多",I35/E35-1,1-I35/E35)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="4" t="n">
         <v>-0.03292357947219116</v>
       </c>
@@ -12780,10 +12898,10 @@
         <v>2914314.34629</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.005422222222222217</v>
+        <v>0.01364444444444457</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0.02377777777777768</v>
+        <v>0.05</v>
       </c>
       <c r="U35" s="19" t="n">
         <v>1.22830388521858</v>
@@ -20902,11 +21020,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C396" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C396" s="2" t="inlineStr"/>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="20" t="n"/>
       <c r="F396" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 04:13（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 07:00（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
@@ -1113,73 +1113,73 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -1188,38 +1188,38 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>442</v>
@@ -1234,61 +1234,61 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
@@ -1303,15 +1303,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
@@ -1326,15 +1326,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
@@ -1349,15 +1349,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
@@ -1366,50 +1366,50 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -1418,15 +1418,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
@@ -1441,15 +1441,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
@@ -1464,15 +1464,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
@@ -1487,15 +1487,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
@@ -1510,61 +1510,61 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
@@ -1573,27 +1573,27 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1</v>
@@ -1607,47 +1607,70 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1811,13 +1834,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5675675675675675</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.005594594594594606</v>
+        <v>-0.005133333333333344</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>36</v>
@@ -9118,7 +9141,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-17 04:13（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-17 07:00（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 07:00（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 09:29（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
@@ -1119,15 +1119,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>440</v>
@@ -1136,73 +1136,73 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -1211,38 +1211,38 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>442</v>
@@ -1257,61 +1257,61 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
@@ -1326,15 +1326,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
@@ -1349,15 +1349,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
@@ -1372,15 +1372,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
@@ -1389,50 +1389,50 @@
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -1441,15 +1441,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
@@ -1464,15 +1464,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
@@ -1487,15 +1487,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
@@ -1510,15 +1510,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
@@ -1533,61 +1533,61 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>442</v>
@@ -1596,27 +1596,27 @@
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1</v>
@@ -1630,47 +1630,70 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1719,7 +1742,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>近 1 個月最佳區間：5%–6%（每筆 +0.61%）</t>
+          <t>近 1 個月最佳區間：8% 以上（每筆 +0.72%）</t>
         </is>
       </c>
     </row>
@@ -1834,22 +1857,22 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5733333333333334</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.005133333333333344</v>
+        <v>-0.003820512820512829</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.000111111111111105</v>
+        <v>-0.0004736842105263221</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>31</v>
@@ -1879,13 +1902,13 @@
         <v>-0.001400000000000006</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.006142857142857143</v>
+        <v>0.007181818181818183</v>
       </c>
     </row>
   </sheetData>
@@ -9141,7 +9164,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-17 07:00（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-17 09:29（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 09:29（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 09:41（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>・持倉時間以1小時K棒為精度（觸價當根收盤計），5分K判定的交易精度為5分鐘。</t>
+          <t>・持倉時間以主K棒為精度（觸價當根收盤計）；同根雙觸發時改用更小週期K棒判定。</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
@@ -1119,15 +1119,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>440</v>
@@ -1142,15 +1142,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>440</v>
@@ -1159,73 +1159,73 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
@@ -1234,38 +1234,38 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>442</v>
@@ -1280,61 +1280,61 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
@@ -1349,15 +1349,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
@@ -1372,15 +1372,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
@@ -1395,15 +1395,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
@@ -1412,50 +1412,50 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -1464,15 +1464,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
@@ -1487,15 +1487,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
@@ -1510,15 +1510,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
@@ -1533,15 +1533,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
@@ -1556,61 +1556,61 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>442</v>
@@ -1619,27 +1619,27 @@
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1</v>
@@ -1653,47 +1653,70 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -9164,7 +9187,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-17 09:29（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-17 09:41（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9181,7 +9204,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1小時</t>
+          <t>60 分鐘</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9261,7 +9284,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>收盤 vs 1小時前收盤</t>
+          <t>收盤 vs 前一根收盤</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9328,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20小時前</t>
+          <t>20 根前</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -9635,7 +9658,7 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>1h漲跌幅</t>
+          <t>前一根漲跌幅</t>
         </is>
       </c>
       <c r="O1" s="3" t="inlineStr">

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,8 +18,8 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$70</f>
+              <f>'資金明細'!$R$2:$R$72</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 09:41（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 15:46（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -811,19 +811,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -831,35 +831,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$35,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$36,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$J$2:$J$35,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$J$2:$J$36,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$J$2:$J$35,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$J$2:$J$36,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$J$2:$J$35,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$J$2:$J$36,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$35,"&lt;&gt;未平倉",交易明細!$L$2:$L$35,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$36,"&lt;&gt;未平倉",交易明細!$L$2:$L$36,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$B$2:$B$35,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$B$2:$B$36,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -878,19 +878,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -898,35 +898,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$35,"做多",交易明細!$J$2:$J$35,"&lt;&gt;未平倉",交易明細!$L$2:$L$35,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"&lt;&gt;未平倉",交易明細!$L$2:$L$36,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$B$2:$B$35,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$B$2:$B$36,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -945,19 +945,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -965,35 +965,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$35,"做空",交易明細!$J$2:$J$35,"&lt;&gt;未平倉",交易明細!$L$2:$L$35,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"&lt;&gt;未平倉",交易明細!$L$2:$L$36,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,33 +1101,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>440</v>
@@ -1142,15 +1142,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>440</v>
@@ -1165,15 +1165,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>440</v>
@@ -1182,73 +1182,73 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -1257,38 +1257,38 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>442</v>
@@ -1303,61 +1303,61 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
@@ -1372,15 +1372,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
@@ -1395,15 +1395,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
@@ -1418,15 +1418,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
@@ -1435,50 +1435,50 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -1487,15 +1487,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
@@ -1510,15 +1510,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
@@ -1533,15 +1533,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
@@ -1556,15 +1556,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
@@ -1579,61 +1579,61 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>442</v>
@@ -1642,27 +1642,27 @@
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1</v>
@@ -1676,47 +1676,70 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1880,13 +1903,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.5949367088607594</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.003820512820512829</v>
+        <v>-0.003405063291139249</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>38</v>
@@ -1898,13 +1921,13 @@
         <v>-0.0004736842105263221</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5625</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.007129032258064522</v>
+        <v>-0.006000000000000005</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>35</v>
@@ -1996,7 +2019,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R70</f>
+        <f>資金明細!R72</f>
         <v/>
       </c>
     </row>
@@ -2034,7 +2057,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$70)</f>
+        <f>MAX(資金明細!$R$2:$R$72)</f>
         <v/>
       </c>
     </row>
@@ -2053,7 +2076,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$70)</f>
+        <f>MIN(資金明細!$R$2:$R$72)</f>
         <v/>
       </c>
     </row>
@@ -2073,7 +2096,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$70)</f>
+        <f>MIN(資金明細!$X$2:$X$72)</f>
         <v/>
       </c>
     </row>
@@ -2092,7 +2115,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$70,"進場",資金明細!$N$2:$N$70,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$72,"進場",資金明細!$N$2:$N$72,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -2111,7 +2134,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$70,"進場",資金明細!$N$2:$N$70,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$72,"進場",資金明細!$N$2:$N$72,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -2122,7 +2145,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$70,"出場",資金明細!$N$2:$N$70,"已下單",資金明細!$K$2:$K$70,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$72,"出場",資金明細!$N$2:$N$72,"已下單",資金明細!$K$2:$K$72,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -2133,7 +2156,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$35),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$36),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2142,7 +2165,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$70,"出場",資金明細!$N$2:$N$70,"已下單",資金明細!$K$2:$K$70,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$72,"出場",資金明細!$N$2:$N$72,"已下單",資金明細!$K$2:$K$72,"止損")</f>
         <v/>
       </c>
     </row>
@@ -2158,7 +2181,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$70,"出場",資金明細!$N$2:$N$70,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$72,"出場",資金明細!$N$2:$N$72,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -2174,7 +2197,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$70)</f>
+        <f>MAX(資金明細!$U$2:$U$72)</f>
         <v/>
       </c>
     </row>
@@ -2190,7 +2213,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$70)</f>
+        <f>MAX(資金明細!$S$2:$S$72)</f>
         <v/>
       </c>
     </row>
@@ -2201,7 +2224,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V70</f>
+        <f>B5*資金明細!V72</f>
         <v/>
       </c>
     </row>
@@ -2223,7 +2246,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$70)</f>
+        <f>MAX(資金明細!$Y$2:$Y$72)</f>
         <v/>
       </c>
     </row>
@@ -2245,7 +2268,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$70,MATCH(1,資金明細!$Z$2:$Z$70,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$72,MATCH(1,資金明細!$Z$2:$Z$72,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -2256,7 +2279,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$70,"進場",資金明細!$N$2:$N$70,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$72,"進場",資金明細!$N$2:$N$72,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -2321,7 +2344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z70"/>
+  <dimension ref="A1:Z72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9104,9 +9127,202 @@
         <v/>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>46282.45833333334</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G71" s="20" t="n">
+        <v>0.24275</v>
+      </c>
+      <c r="H71" s="20" t="n">
+        <v>0.2500325</v>
+      </c>
+      <c r="I71" s="20" t="n">
+        <v>0.2306125</v>
+      </c>
+      <c r="J71" s="20" t="n"/>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="19">
+        <f>資金模擬!$B$5*V70</f>
+        <v/>
+      </c>
+      <c r="N71" s="2">
+        <f>IF(Z70=1,"已停止",IF(T70&gt;=M71,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O71" s="19">
+        <f>IF(N71="已下單",M71*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P71" s="4" t="n"/>
+      <c r="Q71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="13">
+        <f>R70+Q71</f>
+        <v/>
+      </c>
+      <c r="S71" s="19">
+        <f>S70+IF(N71="已下單",M71,0)</f>
+        <v/>
+      </c>
+      <c r="T71" s="19">
+        <f>R71-S71</f>
+        <v/>
+      </c>
+      <c r="U71" s="2">
+        <f>U70+IF(N71="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V71" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R71,0),MAX(V70,FLOOR(MAX(R71,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W71" s="13">
+        <f>MAX(W70,R71)</f>
+        <v/>
+      </c>
+      <c r="X71" s="4">
+        <f>IF(W71&gt;0,R71/W71-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y71" s="19">
+        <f>IF(R71&gt;0,S71*資金模擬!$B$7/R71,0)</f>
+        <v/>
+      </c>
+      <c r="Z71" s="2">
+        <f>IF(OR(Z70=1,R71&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>46282.5</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G72" s="20" t="n">
+        <v>0.24275</v>
+      </c>
+      <c r="H72" s="20" t="n">
+        <v>0.2500325</v>
+      </c>
+      <c r="I72" s="20" t="n">
+        <v>0.2306125</v>
+      </c>
+      <c r="J72" s="20" t="n">
+        <v>0.2500325</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L72" s="5">
+        <f>交易明細!K36</f>
+        <v/>
+      </c>
+      <c r="M72" s="19">
+        <f>M71</f>
+        <v/>
+      </c>
+      <c r="N72" s="2">
+        <f>N71</f>
+        <v/>
+      </c>
+      <c r="O72" s="19">
+        <f>O71</f>
+        <v/>
+      </c>
+      <c r="P72" s="4">
+        <f>交易明細!L36</f>
+        <v/>
+      </c>
+      <c r="Q72" s="13">
+        <f>IF(N72="已下單",O72*P72,0)</f>
+        <v/>
+      </c>
+      <c r="R72" s="13">
+        <f>R71+Q72</f>
+        <v/>
+      </c>
+      <c r="S72" s="19">
+        <f>S71-IF(N72="已下單",M72,0)</f>
+        <v/>
+      </c>
+      <c r="T72" s="19">
+        <f>R72-S72</f>
+        <v/>
+      </c>
+      <c r="U72" s="2">
+        <f>U71-IF(N72="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V72" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R72,0),MAX(V71,FLOOR(MAX(R72,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W72" s="13">
+        <f>MAX(W71,R72)</f>
+        <v/>
+      </c>
+      <c r="X72" s="4">
+        <f>IF(W72&gt;0,R72/W72-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y72" s="19">
+        <f>IF(R72&gt;0,S72*資金模擬!$B$7/R72,0)</f>
+        <v/>
+      </c>
+      <c r="Z72" s="2">
+        <f>IF(OR(Z71=1,R72&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z70"/>
-  <conditionalFormatting sqref="K2:K70">
+  <autoFilter ref="A1:Z72"/>
+  <conditionalFormatting sqref="K2:K72">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -9114,7 +9330,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N70">
+  <conditionalFormatting sqref="N2:N72">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -9122,7 +9338,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q70">
+  <conditionalFormatting sqref="Q2:Q72">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -9187,7 +9403,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-17 09:41（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-17 15:46（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9391,7 +9607,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$35),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$36),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -9556,7 +9772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -13001,9 +13217,105 @@
         <v/>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>USELESS_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>46282.45833333334</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>0.24275</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>0.2500325</v>
+      </c>
+      <c r="G36" s="20" t="n">
+        <v>0.2306125</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>46282.5</v>
+      </c>
+      <c r="I36" s="20" t="n">
+        <v>0.2500325</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K36" s="5">
+        <f>(H36-D36)*24</f>
+        <v/>
+      </c>
+      <c r="L36" s="4">
+        <f>IF(C36="做多",I36/E36-1,1-I36/E36)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="4" t="n">
+        <v>0.03258326598324057</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>0.04022410631062562</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>0.03915172685399226</v>
+      </c>
+      <c r="Q36" s="22" t="n">
+        <v>3772564</v>
+      </c>
+      <c r="R36" s="22" t="n">
+        <v>3887367.54221</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="19" t="n">
+        <v>0.6859164949066544</v>
+      </c>
+      <c r="V36" s="19" t="n">
+        <v>0.8610139860139854</v>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>0.1183074882606505</v>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>0.1027073680385209</v>
+      </c>
+      <c r="Y36" s="4" t="n">
+        <v>0.0001100414096306679</v>
+      </c>
+      <c r="Z36" s="4" t="n">
+        <v>0.005538057160273446</v>
+      </c>
+      <c r="AA36" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB36" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC36" s="4">
+        <f>(AB36+2*參數!$B$7)/(AA36+AB36)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC35"/>
-  <conditionalFormatting sqref="J2:J35">
+  <autoFilter ref="A1:AC36"/>
+  <conditionalFormatting sqref="J2:J36">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -13106,31 +13418,31 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RAY_USDT_PERP</t>
+          <t>USELESS_USDT_PERP</t>
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -13138,50 +13450,50 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A2,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>USELESS_USDT_PERP</t>
+          <t>RAY_USDT_PERP</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -13189,19 +13501,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A3,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13212,27 +13524,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -13240,19 +13552,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A4,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13263,27 +13575,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -13291,19 +13603,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A5,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13314,27 +13626,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -13342,19 +13654,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A6,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13365,27 +13677,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -13393,19 +13705,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A7,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13416,27 +13728,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -13444,19 +13756,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A8,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13467,27 +13779,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -13495,19 +13807,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A9,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13518,27 +13830,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -13546,19 +13858,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A10,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13569,27 +13881,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -13597,19 +13909,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A11,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13620,27 +13932,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -13648,19 +13960,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A12,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13671,27 +13983,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -13699,19 +14011,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A13,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13722,27 +14034,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -13750,19 +14062,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A14,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13773,27 +14085,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -13801,19 +14113,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A15,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13824,27 +14136,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -13852,19 +14164,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A16,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13875,27 +14187,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$C$2:$C$35,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$C$2:$C$36,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$C$2:$C$35,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$C$2:$C$36,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -13903,19 +14215,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$35,交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$35,交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$35,$A17,交易明細!$J$2:$J$35,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"未平倉")</f>
         <v/>
       </c>
     </row>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,8 +18,8 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$72</f>
+              <f>'資金明細'!$R$2:$R$73</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 15:46（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 21:33（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -811,19 +811,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -831,35 +831,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$36,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$37,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$J$2:$J$36,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$J$2:$J$37,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$J$2:$J$36,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$J$2:$J$37,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$J$2:$J$36,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$J$2:$J$37,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$36,"&lt;&gt;未平倉",交易明細!$L$2:$L$36,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$37,"&lt;&gt;未平倉",交易明細!$L$2:$L$37,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$B$2:$B$36,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$B$2:$B$37,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -878,19 +878,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -898,35 +898,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$36,"做多",交易明細!$J$2:$J$36,"&lt;&gt;未平倉",交易明細!$L$2:$L$36,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"&lt;&gt;未平倉",交易明細!$L$2:$L$37,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$B$2:$B$36,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$B$2:$B$37,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -945,19 +945,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -965,35 +965,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$36,"做空",交易明細!$J$2:$J$36,"&lt;&gt;未平倉",交易明細!$L$2:$L$36,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"&lt;&gt;未平倉",交易明細!$L$2:$L$37,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
@@ -1113,44 +1113,44 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>440</v>
@@ -1165,15 +1165,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>440</v>
@@ -1188,15 +1188,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>440</v>
@@ -1205,73 +1205,73 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -1280,38 +1280,38 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>442</v>
@@ -1326,61 +1326,61 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
@@ -1395,15 +1395,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
@@ -1418,15 +1418,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
@@ -1441,15 +1441,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
@@ -1458,50 +1458,50 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1510,15 +1510,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
@@ -1533,15 +1533,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
@@ -1556,15 +1556,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
@@ -1579,15 +1579,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>442</v>
@@ -1602,61 +1602,61 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>442</v>
@@ -1665,27 +1665,27 @@
         <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1</v>
@@ -1699,47 +1699,70 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1788,7 +1811,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>近 1 個月最佳區間：8% 以上（每筆 +0.72%）</t>
+          <t>近 1 個月最佳區間：8% 以上（每筆 +0.81%）</t>
         </is>
       </c>
     </row>
@@ -1948,13 +1971,13 @@
         <v>-0.001400000000000006</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.007181818181818183</v>
+        <v>0.008130434782608697</v>
       </c>
     </row>
   </sheetData>
@@ -2019,7 +2042,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R72</f>
+        <f>資金明細!R73</f>
         <v/>
       </c>
     </row>
@@ -2057,7 +2080,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$72)</f>
+        <f>MAX(資金明細!$R$2:$R$73)</f>
         <v/>
       </c>
     </row>
@@ -2076,7 +2099,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$72)</f>
+        <f>MIN(資金明細!$R$2:$R$73)</f>
         <v/>
       </c>
     </row>
@@ -2096,7 +2119,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$72)</f>
+        <f>MIN(資金明細!$X$2:$X$73)</f>
         <v/>
       </c>
     </row>
@@ -2115,7 +2138,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$72,"進場",資金明細!$N$2:$N$72,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$73,"進場",資金明細!$N$2:$N$73,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -2134,7 +2157,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$72,"進場",資金明細!$N$2:$N$72,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$73,"進場",資金明細!$N$2:$N$73,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -2145,7 +2168,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$72,"出場",資金明細!$N$2:$N$72,"已下單",資金明細!$K$2:$K$72,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$73,"出場",資金明細!$N$2:$N$73,"已下單",資金明細!$K$2:$K$73,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -2156,7 +2179,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$36),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$37),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2165,7 +2188,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$72,"出場",資金明細!$N$2:$N$72,"已下單",資金明細!$K$2:$K$72,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$73,"出場",資金明細!$N$2:$N$73,"已下單",資金明細!$K$2:$K$73,"止損")</f>
         <v/>
       </c>
     </row>
@@ -2181,7 +2204,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$72,"出場",資金明細!$N$2:$N$72,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$73,"出場",資金明細!$N$2:$N$73,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -2197,7 +2220,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$72)</f>
+        <f>MAX(資金明細!$U$2:$U$73)</f>
         <v/>
       </c>
     </row>
@@ -2213,7 +2236,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$72)</f>
+        <f>MAX(資金明細!$S$2:$S$73)</f>
         <v/>
       </c>
     </row>
@@ -2224,7 +2247,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V72</f>
+        <f>B5*資金明細!V73</f>
         <v/>
       </c>
     </row>
@@ -2235,7 +2258,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>0</f>
+        <f>IF(資金明細!N73="已下單",資金明細!O73*交易明細!L37,0)</f>
         <v/>
       </c>
     </row>
@@ -2246,7 +2269,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$72)</f>
+        <f>MAX(資金明細!$Y$2:$Y$73)</f>
         <v/>
       </c>
     </row>
@@ -2268,7 +2291,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$72,MATCH(1,資金明細!$Z$2:$Z$72,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$73,MATCH(1,資金明細!$Z$2:$Z$73,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -2279,7 +2302,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$72,"進場",資金明細!$N$2:$N$72,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$73,"進場",資金明細!$N$2:$N$73,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -2344,7 +2367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z72"/>
+  <dimension ref="A1:Z73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9320,9 +9343,103 @@
         <v/>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>46282.83333333334</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="n">
+        <v>0.10472</v>
+      </c>
+      <c r="H73" s="20" t="n">
+        <v>0.1015784</v>
+      </c>
+      <c r="I73" s="20" t="n">
+        <v>0.109956</v>
+      </c>
+      <c r="J73" s="20" t="n"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="n"/>
+      <c r="M73" s="19">
+        <f>資金模擬!$B$5*V72</f>
+        <v/>
+      </c>
+      <c r="N73" s="2">
+        <f>IF(Z72=1,"已停止",IF(T72&gt;=M73,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O73" s="19">
+        <f>IF(N73="已下單",M73*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P73" s="4" t="n"/>
+      <c r="Q73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="13">
+        <f>R72+Q73</f>
+        <v/>
+      </c>
+      <c r="S73" s="19">
+        <f>S72+IF(N73="已下單",M73,0)</f>
+        <v/>
+      </c>
+      <c r="T73" s="19">
+        <f>R73-S73</f>
+        <v/>
+      </c>
+      <c r="U73" s="2">
+        <f>U72+IF(N73="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V73" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R73,0),MAX(V72,FLOOR(MAX(R73,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W73" s="13">
+        <f>MAX(W72,R73)</f>
+        <v/>
+      </c>
+      <c r="X73" s="4">
+        <f>IF(W73&gt;0,R73/W73-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y73" s="19">
+        <f>IF(R73&gt;0,S73*資金模擬!$B$7/R73,0)</f>
+        <v/>
+      </c>
+      <c r="Z73" s="2">
+        <f>IF(OR(Z72=1,R73&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z72"/>
-  <conditionalFormatting sqref="K2:K72">
+  <autoFilter ref="A1:Z73"/>
+  <conditionalFormatting sqref="K2:K73">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -9330,7 +9447,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N72">
+  <conditionalFormatting sqref="N2:N73">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -9338,7 +9455,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q72">
+  <conditionalFormatting sqref="Q2:Q73">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -9403,7 +9520,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-17 15:46（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-17 21:33（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9607,7 +9724,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$36),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$37),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -9772,7 +9889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -13313,9 +13430,109 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>46282.83333333334</v>
+      </c>
+      <c r="E37" s="20" t="n">
+        <v>0.10472</v>
+      </c>
+      <c r="F37" s="20" t="n">
+        <v>0.1015784</v>
+      </c>
+      <c r="G37" s="20" t="n">
+        <v>0.109956</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>46282.875</v>
+      </c>
+      <c r="I37" s="20" t="n">
+        <v>0.10548</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K37" s="5">
+        <f>(H37-D37)*24</f>
+        <v/>
+      </c>
+      <c r="L37" s="4">
+        <f>IF(C37="做多",I37/E37-1,1-I37/E37)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>-0.04172767203513916</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0.04048676979687356</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>-0.006338482559684278</v>
+      </c>
+      <c r="Q37" s="22" t="n">
+        <v>-4050075</v>
+      </c>
+      <c r="R37" s="22" t="n">
+        <v>2337042.32057</v>
+      </c>
+      <c r="S37" s="4" t="n">
+        <v>0.0003819709702062024</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>0.02053093964858688</v>
+      </c>
+      <c r="U37" s="19" t="n">
+        <v>0.3772019483351589</v>
+      </c>
+      <c r="V37" s="19" t="n">
+        <v>0.9287090558766868</v>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>0.08628786120510201</v>
+      </c>
+      <c r="X37" s="4" t="n">
+        <v>0.06791277258566986</v>
+      </c>
+      <c r="Y37" s="4" t="n">
+        <v>-0.0009859272953907094</v>
+      </c>
+      <c r="Z37" s="4" t="n">
+        <v>-0.003379461603953526</v>
+      </c>
+      <c r="AA37" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB37" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC37" s="4">
+        <f>(AB37+2*參數!$B$7)/(AA37+AB37)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC36"/>
-  <conditionalFormatting sqref="J2:J36">
+  <autoFilter ref="A1:AC37"/>
+  <conditionalFormatting sqref="J2:J37">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -13422,27 +13639,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -13450,19 +13667,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A2,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13473,27 +13690,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -13501,19 +13718,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A3,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13524,27 +13741,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -13552,19 +13769,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A4,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13575,27 +13792,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -13603,19 +13820,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A5,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13626,27 +13843,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -13654,50 +13871,50 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A6,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HEMI_USDT_PERP</t>
+          <t>牛来_USDT_PERP</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -13705,50 +13922,50 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A7,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BULLA_USDT_PERP</t>
+          <t>HEMI_USDT_PERP</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -13756,50 +13973,50 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A8,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RIVER_USDT_PERP</t>
+          <t>BULLA_USDT_PERP</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -13807,50 +14024,50 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A9,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>牛来_USDT_PERP</t>
+          <t>RIVER_USDT_PERP</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -13858,19 +14075,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A10,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13881,27 +14098,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -13909,19 +14126,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A11,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13932,27 +14149,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -13960,19 +14177,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A12,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13983,27 +14200,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -14011,19 +14228,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A13,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -14034,27 +14251,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -14062,19 +14279,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A14,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -14085,27 +14302,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -14113,19 +14330,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A15,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -14136,27 +14353,27 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -14164,19 +14381,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A16,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -14187,27 +14404,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$C$2:$C$36,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$C$2:$C$37,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$C$2:$C$36,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$C$2:$C$37,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -14215,19 +14432,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$36,交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$36,交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$36,$A17,交易明細!$J$2:$J$36,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -22247,7 +22464,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr"/>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="20" t="n"/>
       <c r="F443" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,7 +18,7 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$73</f>
+              <f>'資金明細'!$R$2:$R$74</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-17 21:33（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-18 02:18（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,33 +1101,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>440</v>
@@ -1136,44 +1136,44 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>440</v>
@@ -1188,15 +1188,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>440</v>
@@ -1211,15 +1211,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>440</v>
@@ -1228,73 +1228,73 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
@@ -1303,38 +1303,38 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>442</v>
@@ -1349,61 +1349,61 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
@@ -1418,15 +1418,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
@@ -1441,15 +1441,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
@@ -1464,15 +1464,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
@@ -1481,50 +1481,50 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -1533,15 +1533,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
@@ -1556,15 +1556,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
@@ -1579,15 +1579,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>442</v>
@@ -1602,15 +1602,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>442</v>
@@ -1625,61 +1625,61 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>442</v>
@@ -1688,27 +1688,27 @@
         <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1</v>
@@ -1722,47 +1722,70 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1811,7 +1834,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>近 1 個月最佳區間：8% 以上（每筆 +0.81%）</t>
+          <t>近 1 個月最佳區間：8% 以上（每筆 +0.98%）</t>
         </is>
       </c>
     </row>
@@ -1926,31 +1949,31 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5949367088607594</v>
+        <v>0.6144578313253012</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.003405063291139249</v>
+        <v>-0.001843373493975911</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6410256410256411</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.0004736842105263221</v>
+        <v>0.0002820512820512766</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.5625</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.006000000000000005</v>
+        <v>-0.00736363636363637</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>35</v>
@@ -1971,13 +1994,13 @@
         <v>-0.001400000000000006</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.76</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.008130434782608697</v>
+        <v>0.009800000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -2042,7 +2065,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R73</f>
+        <f>資金明細!R74</f>
         <v/>
       </c>
     </row>
@@ -2080,7 +2103,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$73)</f>
+        <f>MAX(資金明細!$R$2:$R$74)</f>
         <v/>
       </c>
     </row>
@@ -2099,7 +2122,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$73)</f>
+        <f>MIN(資金明細!$R$2:$R$74)</f>
         <v/>
       </c>
     </row>
@@ -2119,7 +2142,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$73)</f>
+        <f>MIN(資金明細!$X$2:$X$74)</f>
         <v/>
       </c>
     </row>
@@ -2138,7 +2161,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$73,"進場",資金明細!$N$2:$N$73,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$74,"進場",資金明細!$N$2:$N$74,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -2157,7 +2180,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$73,"進場",資金明細!$N$2:$N$73,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$74,"進場",資金明細!$N$2:$N$74,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -2168,7 +2191,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$73,"出場",資金明細!$N$2:$N$73,"已下單",資金明細!$K$2:$K$73,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$74,"出場",資金明細!$N$2:$N$74,"已下單",資金明細!$K$2:$K$74,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -2188,7 +2211,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$73,"出場",資金明細!$N$2:$N$73,"已下單",資金明細!$K$2:$K$73,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$74,"出場",資金明細!$N$2:$N$74,"已下單",資金明細!$K$2:$K$74,"止損")</f>
         <v/>
       </c>
     </row>
@@ -2204,7 +2227,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$73,"出場",資金明細!$N$2:$N$73,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$74,"出場",資金明細!$N$2:$N$74,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -2220,7 +2243,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$73)</f>
+        <f>MAX(資金明細!$U$2:$U$74)</f>
         <v/>
       </c>
     </row>
@@ -2236,7 +2259,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$73)</f>
+        <f>MAX(資金明細!$S$2:$S$74)</f>
         <v/>
       </c>
     </row>
@@ -2247,7 +2270,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V73</f>
+        <f>B5*資金明細!V74</f>
         <v/>
       </c>
     </row>
@@ -2258,7 +2281,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>IF(資金明細!N73="已下單",資金明細!O73*交易明細!L37,0)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -2269,7 +2292,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$73)</f>
+        <f>MAX(資金明細!$Y$2:$Y$74)</f>
         <v/>
       </c>
     </row>
@@ -2291,7 +2314,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$73,MATCH(1,資金明細!$Z$2:$Z$73,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$74,MATCH(1,資金明細!$Z$2:$Z$74,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -2302,7 +2325,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$73,"進場",資金明細!$N$2:$N$73,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$74,"進場",資金明細!$N$2:$N$74,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -2367,7 +2390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z73"/>
+  <dimension ref="A1:Z74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9378,11 +9401,7 @@
         <v>0.109956</v>
       </c>
       <c r="J73" s="20" t="n"/>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K73" s="2" t="n"/>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="19">
         <f>資金模擬!$B$5*V72</f>
@@ -9437,9 +9456,112 @@
         <v/>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>46282.91666666666</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>牛来_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G74" s="20" t="n">
+        <v>0.10472</v>
+      </c>
+      <c r="H74" s="20" t="n">
+        <v>0.1015784</v>
+      </c>
+      <c r="I74" s="20" t="n">
+        <v>0.109956</v>
+      </c>
+      <c r="J74" s="20" t="n">
+        <v>0.109956</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L74" s="5">
+        <f>交易明細!K37</f>
+        <v/>
+      </c>
+      <c r="M74" s="19">
+        <f>M73</f>
+        <v/>
+      </c>
+      <c r="N74" s="2">
+        <f>N73</f>
+        <v/>
+      </c>
+      <c r="O74" s="19">
+        <f>O73</f>
+        <v/>
+      </c>
+      <c r="P74" s="4">
+        <f>交易明細!L37</f>
+        <v/>
+      </c>
+      <c r="Q74" s="13">
+        <f>IF(N74="已下單",O74*P74,0)</f>
+        <v/>
+      </c>
+      <c r="R74" s="13">
+        <f>R73+Q74</f>
+        <v/>
+      </c>
+      <c r="S74" s="19">
+        <f>S73-IF(N74="已下單",M74,0)</f>
+        <v/>
+      </c>
+      <c r="T74" s="19">
+        <f>R74-S74</f>
+        <v/>
+      </c>
+      <c r="U74" s="2">
+        <f>U73-IF(N74="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V74" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R74,0),MAX(V73,FLOOR(MAX(R74,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W74" s="13">
+        <f>MAX(W73,R74)</f>
+        <v/>
+      </c>
+      <c r="X74" s="4">
+        <f>IF(W74&gt;0,R74/W74-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y74" s="19">
+        <f>IF(R74&gt;0,S74*資金模擬!$B$7/R74,0)</f>
+        <v/>
+      </c>
+      <c r="Z74" s="2">
+        <f>IF(OR(Z73=1,R74&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z73"/>
-  <conditionalFormatting sqref="K2:K73">
+  <autoFilter ref="A1:Z74"/>
+  <conditionalFormatting sqref="K2:K74">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -9447,7 +9569,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N73">
+  <conditionalFormatting sqref="N2:N74">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -9455,7 +9577,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q73">
+  <conditionalFormatting sqref="Q2:Q74">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -9520,7 +9642,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-17 21:33（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-18 02:18（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -13457,14 +13579,14 @@
         <v>0.109956</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>46282.875</v>
+        <v>46282.91666666666</v>
       </c>
       <c r="I37" s="20" t="n">
-        <v>0.10548</v>
+        <v>0.109956</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K37" s="5">
@@ -13475,11 +13597,7 @@
         <f>IF(C37="做多",I37/E37-1,1-I37/E37)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="4" t="n">
         <v>-0.04172767203513916</v>
       </c>
@@ -13499,7 +13617,7 @@
         <v>0.0003819709702062024</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>0.02053093964858688</v>
+        <v>0.05</v>
       </c>
       <c r="U37" s="19" t="n">
         <v>0.3772019483351589</v>
@@ -22464,11 +22582,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C443" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C443" s="2" t="inlineStr"/>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="20" t="n"/>
       <c r="F443" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -18,8 +18,8 @@
     <sheet name="掃描清單" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資金明細'!$A$1:$Z$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'交易明細'!$A$1:$AC$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'幣種統計'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'掃描清單'!$A$1:$H$443</definedName>
   </definedNames>
@@ -296,7 +296,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$74</f>
+              <f>'資金明細'!$R$2:$R$75</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-18 02:18（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-18 06:14（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -811,19 +811,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -831,35 +831,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$37,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$38,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$J$2:$J$37,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$J$2:$J$38,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$J$2:$J$37,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$J$2:$J$38,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$J$2:$J$37,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$J$2:$J$38,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$37,"&lt;&gt;未平倉",交易明細!$L$2:$L$37,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$38,"&lt;&gt;未平倉",交易明細!$L$2:$L$38,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$B$2:$B$37,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$38,"做多",交易明細!$B$2:$B$38,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -878,19 +878,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -898,35 +898,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$38,交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$37,"做多",交易明細!$J$2:$J$37,"&lt;&gt;未平倉",交易明細!$L$2:$L$37,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$38,"做多",交易明細!$J$2:$J$38,"&lt;&gt;未平倉",交易明細!$L$2:$L$38,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$B$2:$B$37,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$38,"做空",交易明細!$B$2:$B$38,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -945,19 +945,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -965,35 +965,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$38,交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$37,"做空",交易明細!$J$2:$J$37,"&lt;&gt;未平倉",交易明細!$L$2:$L$37,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$38,"做空",交易明細!$J$2:$J$38,"&lt;&gt;未平倉",交易明細!$L$2:$L$38,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,56 +1101,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>440</v>
@@ -1159,44 +1159,44 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>440</v>
@@ -1211,15 +1211,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>440</v>
@@ -1234,15 +1234,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>440</v>
@@ -1251,73 +1251,73 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -1326,38 +1326,38 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>442</v>
@@ -1372,61 +1372,61 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
@@ -1441,15 +1441,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
@@ -1464,15 +1464,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
@@ -1487,15 +1487,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
@@ -1504,50 +1504,50 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -1556,15 +1556,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
@@ -1579,15 +1579,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>442</v>
@@ -1602,15 +1602,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>442</v>
@@ -1625,15 +1625,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>442</v>
@@ -1648,61 +1648,61 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>442</v>
@@ -1711,27 +1711,27 @@
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1</v>
@@ -1745,47 +1745,70 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -2065,7 +2088,7 @@
         </is>
       </c>
       <c r="E4" s="13">
-        <f>資金明細!R74</f>
+        <f>資金明細!R75</f>
         <v/>
       </c>
     </row>
@@ -2103,7 +2126,7 @@
         </is>
       </c>
       <c r="E6" s="13">
-        <f>MAX(資金明細!$R$2:$R$74)</f>
+        <f>MAX(資金明細!$R$2:$R$75)</f>
         <v/>
       </c>
     </row>
@@ -2122,7 +2145,7 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>MIN(資金明細!$R$2:$R$74)</f>
+        <f>MIN(資金明細!$R$2:$R$75)</f>
         <v/>
       </c>
     </row>
@@ -2142,7 +2165,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$74)</f>
+        <f>MIN(資金明細!$X$2:$X$75)</f>
         <v/>
       </c>
     </row>
@@ -2161,7 +2184,7 @@
         </is>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$74,"進場",資金明細!$N$2:$N$74,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$75,"進場",資金明細!$N$2:$N$75,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -2180,7 +2203,7 @@
         </is>
       </c>
       <c r="E10" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$74,"進場",資金明細!$N$2:$N$74,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$75,"進場",資金明細!$N$2:$N$75,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -2191,7 +2214,7 @@
         </is>
       </c>
       <c r="E11" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$74,"出場",資金明細!$N$2:$N$74,"已下單",資金明細!$K$2:$K$74,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$75,"出場",資金明細!$N$2:$N$75,"已下單",資金明細!$K$2:$K$75,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -2202,7 +2225,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$37),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$38),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2211,7 +2234,7 @@
         </is>
       </c>
       <c r="E12" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$74,"出場",資金明細!$N$2:$N$74,"已下單",資金明細!$K$2:$K$74,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$75,"出場",資金明細!$N$2:$N$75,"已下單",資金明細!$K$2:$K$75,"止損")</f>
         <v/>
       </c>
     </row>
@@ -2227,7 +2250,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$74,"出場",資金明細!$N$2:$N$74,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$75,"出場",資金明細!$N$2:$N$75,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2266,7 @@
         </is>
       </c>
       <c r="E14" s="18">
-        <f>MAX(資金明細!$U$2:$U$74)</f>
+        <f>MAX(資金明細!$U$2:$U$75)</f>
         <v/>
       </c>
     </row>
@@ -2259,7 +2282,7 @@
         </is>
       </c>
       <c r="E15" s="19">
-        <f>MAX(資金明細!$S$2:$S$74)</f>
+        <f>MAX(資金明細!$S$2:$S$75)</f>
         <v/>
       </c>
     </row>
@@ -2270,7 +2293,7 @@
         </is>
       </c>
       <c r="E16" s="19">
-        <f>B5*資金明細!V74</f>
+        <f>B5*資金明細!V75</f>
         <v/>
       </c>
     </row>
@@ -2281,7 +2304,7 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>0</f>
+        <f>IF(資金明細!N75="已下單",資金明細!O75*交易明細!L38,0)</f>
         <v/>
       </c>
     </row>
@@ -2292,7 +2315,7 @@
         </is>
       </c>
       <c r="E18" s="19">
-        <f>MAX(資金明細!$Y$2:$Y$74)</f>
+        <f>MAX(資金明細!$Y$2:$Y$75)</f>
         <v/>
       </c>
     </row>
@@ -2314,7 +2337,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$74,MATCH(1,資金明細!$Z$2:$Z$74,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$75,MATCH(1,資金明細!$Z$2:$Z$75,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -2325,7 +2348,7 @@
         </is>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS(資金明細!$C$2:$C$74,"進場",資金明細!$N$2:$N$74,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$75,"進場",資金明細!$N$2:$N$75,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -2390,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z74"/>
+  <dimension ref="A1:Z75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9559,9 +9582,103 @@
         <v/>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>46283.20833333334</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>AKE_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="G75" s="20" t="n">
+        <v>0.0214905</v>
+      </c>
+      <c r="H75" s="20" t="n">
+        <v>0.022135215</v>
+      </c>
+      <c r="I75" s="20" t="n">
+        <v>0.020415975</v>
+      </c>
+      <c r="J75" s="20" t="n"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="n"/>
+      <c r="M75" s="19">
+        <f>資金模擬!$B$5*V74</f>
+        <v/>
+      </c>
+      <c r="N75" s="2">
+        <f>IF(Z74=1,"已停止",IF(T74&gt;=M75,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O75" s="19">
+        <f>IF(N75="已下單",M75*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P75" s="4" t="n"/>
+      <c r="Q75" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="13">
+        <f>R74+Q75</f>
+        <v/>
+      </c>
+      <c r="S75" s="19">
+        <f>S74+IF(N75="已下單",M75,0)</f>
+        <v/>
+      </c>
+      <c r="T75" s="19">
+        <f>R75-S75</f>
+        <v/>
+      </c>
+      <c r="U75" s="2">
+        <f>U74+IF(N75="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V75" s="19">
+        <f>IF(資金模擬!$B$9=2,MAX(R75,0),MAX(V74,FLOOR(MAX(R75,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W75" s="13">
+        <f>MAX(W74,R75)</f>
+        <v/>
+      </c>
+      <c r="X75" s="4">
+        <f>IF(W75&gt;0,R75/W75-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y75" s="19">
+        <f>IF(R75&gt;0,S75*資金模擬!$B$7/R75,0)</f>
+        <v/>
+      </c>
+      <c r="Z75" s="2">
+        <f>IF(OR(Z74=1,R75&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z74"/>
-  <conditionalFormatting sqref="K2:K74">
+  <autoFilter ref="A1:Z75"/>
+  <conditionalFormatting sqref="K2:K75">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -9569,7 +9686,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N74">
+  <conditionalFormatting sqref="N2:N75">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -9577,7 +9694,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q74">
+  <conditionalFormatting sqref="Q2:Q75">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -9642,7 +9759,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-18 02:18（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-18 06:14（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9846,7 +9963,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$37),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$38),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10011,7 +10128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -13648,9 +13765,109 @@
         <v/>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>AKE_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>做多</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>46283.20833333334</v>
+      </c>
+      <c r="E38" s="20" t="n">
+        <v>0.0214905</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>0.022135215</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>0.020415975</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>46283.25</v>
+      </c>
+      <c r="I38" s="20" t="n">
+        <v>0.0210955</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K38" s="5">
+        <f>(H38-D38)*24</f>
+        <v/>
+      </c>
+      <c r="L38" s="4">
+        <f>IF(C38="做多",I38/E38-1,1-I38/E38)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0.02601990881096183</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0.04972128367543062</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0.0241716031320145</v>
+      </c>
+      <c r="Q38" s="22" t="n">
+        <v>5592380</v>
+      </c>
+      <c r="R38" s="22" t="n">
+        <v>1554549.0829196</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>0.0004187896977734251</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>0.02131174239780365</v>
+      </c>
+      <c r="U38" s="19" t="n">
+        <v>0.5059324416336631</v>
+      </c>
+      <c r="V38" s="19" t="n">
+        <v>0.6913765131661026</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>0.03822742709846749</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>0.111223144341891</v>
+      </c>
+      <c r="Y38" s="4" t="n">
+        <v>-0.0003996823439672559</v>
+      </c>
+      <c r="Z38" s="4" t="n">
+        <v>0.0002900349911074684</v>
+      </c>
+      <c r="AA38" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB38" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC38" s="4">
+        <f>(AB38+2*參數!$B$7)/(AA38+AB38)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC37"/>
-  <conditionalFormatting sqref="J2:J37">
+  <autoFilter ref="A1:AC38"/>
+  <conditionalFormatting sqref="J2:J38">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -13757,27 +13974,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A2,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A2,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$38,$A2,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A2,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A2,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -13785,19 +14002,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A2,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A2,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A2,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A2,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A2,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13808,27 +14025,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A3,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A3,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$38,$A3,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A3,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A3,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -13836,19 +14053,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A3,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A3,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A3,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A3,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A3,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13859,27 +14076,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A4,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A4,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$38,$A4,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A4,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A4,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -13887,19 +14104,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A4,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A4,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A4,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A4,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A4,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13910,27 +14127,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A5,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A5,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$38,$A5,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A5,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A5,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -13938,19 +14155,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A5,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A5,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A5,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A5,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A5,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -13961,27 +14178,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A6,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A6,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$38,$A6,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A6,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A6,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -13989,19 +14206,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A6,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A6,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A6,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A6,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A6,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -14012,27 +14229,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A7,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A7,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$38,$A7,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A7,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A7,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -14040,19 +14257,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A7,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A7,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A7,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A7,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A7,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -14063,27 +14280,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A8,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A8,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$38,$A8,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A8,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A8,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -14091,19 +14308,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A8,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A8,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A8,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A8,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A8,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -14114,27 +14331,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A9,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A9,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$38,$A9,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A9,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A9,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -14142,50 +14359,50 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A9,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A9,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A9,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A9,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A9,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RIVER_USDT_PERP</t>
+          <t>AKE_USDT_PERP</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A10,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A10,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$38,$A10,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A10,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A10,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -14193,50 +14410,50 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A10,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A10,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A10,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A10,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A10,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ACE_USDT_PERP</t>
+          <t>RIVER_USDT_PERP</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A11,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A11,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$38,$A11,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A11,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A11,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -14244,50 +14461,50 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A11,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A11,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A11,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A11,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A11,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ARB_USDT_PERP</t>
+          <t>ACE_USDT_PERP</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A12,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A12,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$38,$A12,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A12,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A12,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -14295,50 +14512,50 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A12,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A12,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A12,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A12,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A12,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DASH_USDT_PERP</t>
+          <t>ARB_USDT_PERP</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A13,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A13,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$38,$A13,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A13,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A13,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -14346,50 +14563,50 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A13,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A13,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A13,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A13,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A13,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>IOST_USDT_PERP</t>
+          <t>DASH_USDT_PERP</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A14,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A14,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$38,$A14,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A14,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A14,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -14397,50 +14614,50 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A14,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A14,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A14,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A14,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A14,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CASHCAT_USDT_PERP</t>
+          <t>IOST_USDT_PERP</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A15,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A15,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$38,$A15,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A15,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A15,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -14448,50 +14665,50 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A15,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A15,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A15,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A15,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A15,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AKE_USDT_PERP</t>
+          <t>CASHCAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A16,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A16,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$38,$A16,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A16,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A16,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H16" s="4">
@@ -14499,19 +14716,19 @@
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A16,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A16,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A16,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L16" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A16,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A16,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -14522,27 +14739,27 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$C$2:$C$37,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A17,交易明細!$C$2:$C$38,"做多")</f>
         <v/>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$C$2:$C$37,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A17,交易明細!$C$2:$C$38,"做空")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"時間出場")</f>
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$38,$A17,交易明細!$J$2:$J$38,"時間出場")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A17,交易明細!$J$2:$J$38,"止盈")</f>
         <v/>
       </c>
       <c r="G17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A17,交易明細!$J$2:$J$38,"止損")</f>
         <v/>
       </c>
       <c r="H17" s="4">
@@ -14550,19 +14767,19 @@
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A17,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$37,交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$38,交易明細!$B$2:$B$38,$A17,交易明細!$J$2:$J$38,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$37,交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$38,交易明細!$B$2:$B$38,$A17,交易明細!$J$2:$J$38,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L17" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$37,$A17,交易明細!$J$2:$J$37,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$38,$A17,交易明細!$J$2:$J$38,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -14986,7 +15203,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="20" t="n"/>
       <c r="F21" s="20" t="n"/>

--- a/output/dryrun_main.xlsx
+++ b/output/dryrun_main.xlsx
@@ -710,7 +710,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-18 06:14（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-18 08:27（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1101,16 +1101,16 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -1119,61 +1119,61 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>440</v>
@@ -1182,44 +1182,44 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>440</v>
@@ -1234,15 +1234,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>440</v>
@@ -1257,15 +1257,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>440</v>
@@ -1274,73 +1274,73 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>440</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
@@ -1349,38 +1349,38 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>442</v>
@@ -1395,61 +1395,61 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>442</v>
@@ -1464,15 +1464,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>442</v>
@@ -1487,15 +1487,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>442</v>
@@ -1510,15 +1510,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>442</v>
@@ -1527,50 +1527,50 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -1579,15 +1579,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>442</v>
@@ -1602,15 +1602,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>442</v>
@@ -1625,15 +1625,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>442</v>
@@ -1648,15 +1648,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>442</v>
@@ -1671,61 +1671,61 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>442</v>
@@ -1734,27 +1734,27 @@
         <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1</v>
@@ -1768,47 +1768,70 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>442</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1981,13 +2004,13 @@
         <v>-0.001843373493975911</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.65</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0002820512820512766</v>
+        <v>0.0009999999999999953</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>33</v>
@@ -9759,7 +9782,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-18 06:14（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-18 08:27（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -13792,10 +13815,10 @@
         <v>0.020415975</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>46283.25</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="I38" s="20" t="n">
-        <v>0.0210955</v>
+        <v>0.0212875</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -13834,7 +13857,7 @@
         <v>0.0004187896977734251</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>0.02131174239780365</v>
+        <v>0.0264256299295037</v>
       </c>
       <c r="U38" s="19" t="n">
         <v>0.5059324416336631</v>
